--- a/data.xlsx
+++ b/data.xlsx
@@ -54187,15 +54187,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CFB2F24-829F-4D5B-9EB0-E261189A0819}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A1E5B5D-04A9-44F8-BDC1-A1CF40A7D271}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{425A0947-A89D-4F60-B701-6B6C9110ED81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A3D0802-6E62-44EF-9689-88741942C570}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{614FB914-D9BD-419A-BD8C-9B997AC88862}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E3D562-33C5-4C2A-972E-2D7AD8817191}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y603"/>
+  <dimension ref="A1:Y604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66465,7 +66465,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>1216672722760559</t>
+          <t>1216739682296057</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -66480,29 +66480,29 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Mansi Aggarwal</t>
         </is>
       </c>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Julian Komimbin</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>2026-07-17 16:06:47</t>
+          <t>2026-07-20 21:13:35</t>
         </is>
       </c>
       <c r="H597" t="inlineStr"/>
       <c r="I597" t="inlineStr">
         <is>
-          <t>2026-07-21 09:18:14</t>
+          <t>2026-07-21 17:25:43</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>2026-07-21 09:18:14</t>
+          <t>2026-07-21 17:25:18</t>
         </is>
       </c>
       <c r="K597" t="b">
@@ -66510,33 +66510,33 @@
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>New Thryv Social Ads</t>
+          <t>SaaS Add-On</t>
         </is>
       </c>
       <c r="M597" t="inlineStr">
         <is>
-          <t>BSCB8068</t>
+          <t>BSGC2255</t>
         </is>
       </c>
       <c r="N597" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="P597" t="n">
         <v>0</v>
       </c>
       <c r="Q597" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="R597" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Mansi Aggarwal</t>
         </is>
       </c>
       <c r="S597" t="inlineStr">
@@ -66546,7 +66546,7 @@
       </c>
       <c r="T597" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U597" t="inlineStr">
@@ -66556,27 +66556,27 @@
       </c>
       <c r="V597" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W597" t="inlineStr">
         <is>
-          <t>de846yo0m1x1y83t</t>
+          <t>LOC162FA8667</t>
         </is>
       </c>
       <c r="X597" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="Y597" t="inlineStr">
         <is>
-          <t>Stroud Chiropractic PLLC</t>
+          <t>TTW tilers trade warehouse</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>1216669020714116</t>
+          <t>1216672722760559</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -66591,33 +66591,29 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Madison McCaskey</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>2026-07-17 13:14:42</t>
-        </is>
-      </c>
-      <c r="H598" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+          <t>2026-07-17 16:06:47</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr"/>
       <c r="I598" t="inlineStr">
         <is>
-          <t>2026-07-20 21:08:53</t>
+          <t>2026-07-21 09:18:14</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>2026-07-20 21:08:51</t>
+          <t>2026-07-21 09:18:14</t>
         </is>
       </c>
       <c r="K598" t="b">
@@ -66625,33 +66621,33 @@
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>New Thryv Social Ads</t>
         </is>
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>BRWJ6635</t>
+          <t>BSCB8068</t>
         </is>
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="P598" t="n">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="Q598" t="n">
-        <v>6700</v>
+        <v>500</v>
       </c>
       <c r="R598" t="inlineStr">
         <is>
-          <t>Madison McCaskey</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="S598" t="inlineStr">
@@ -66676,22 +66672,22 @@
       </c>
       <c r="W598" t="inlineStr">
         <is>
-          <t>awtjpp33s3vhq5t2</t>
+          <t>de846yo0m1x1y83t</t>
         </is>
       </c>
       <c r="X598" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="Y598" t="inlineStr">
         <is>
-          <t>Boone Heating &amp; Air Conditioning Inc</t>
+          <t>Stroud Chiropractic PLLC</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>1216720207491318</t>
+          <t>1216669020714116</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -66706,7 +66702,7 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>David Ostendorf</t>
+          <t>Madison McCaskey</t>
         </is>
       </c>
       <c r="E599" t="inlineStr"/>
@@ -66717,7 +66713,7 @@
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>2026-07-20 08:18:44</t>
+          <t>2026-07-17 13:14:42</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -66727,12 +66723,12 @@
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>2026-07-20 21:05:39</t>
+          <t>2026-07-20 21:08:53</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>2026-07-20 21:05:37</t>
+          <t>2026-07-20 21:08:51</t>
         </is>
       </c>
       <c r="K599" t="b">
@@ -66745,28 +66741,28 @@
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>BRTH5137</t>
+          <t>BRWJ6635</t>
         </is>
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="P599" t="n">
-        <v>9200</v>
+        <v>5200</v>
       </c>
       <c r="Q599" t="n">
-        <v>10700</v>
+        <v>6700</v>
       </c>
       <c r="R599" t="inlineStr">
         <is>
-          <t>David Ostendorf</t>
+          <t>Madison McCaskey</t>
         </is>
       </c>
       <c r="S599" t="inlineStr">
@@ -66776,7 +66772,7 @@
       </c>
       <c r="T599" t="inlineStr">
         <is>
-          <t>Recommendation sent via email and closed by BA</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U599" t="inlineStr">
@@ -66791,7 +66787,7 @@
       </c>
       <c r="W599" t="inlineStr">
         <is>
-          <t>nwurayxntxfif89x</t>
+          <t>awtjpp33s3vhq5t2</t>
         </is>
       </c>
       <c r="X599" t="n">
@@ -66799,14 +66795,14 @@
       </c>
       <c r="Y599" t="inlineStr">
         <is>
-          <t>Action Glass &amp; Mirror Inc</t>
+          <t>Boone Heating &amp; Air Conditioning Inc</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>1216730477297012</t>
+          <t>1216720207491318</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -66821,29 +66817,33 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Will King</t>
+          <t>David Ostendorf</t>
         </is>
       </c>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Dexter Tardy</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>2026-07-20 12:30:59</t>
-        </is>
-      </c>
-      <c r="H600" t="inlineStr"/>
+          <t>2026-07-20 08:18:44</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>2026-07-20 13:27:50</t>
+          <t>2026-07-20 21:05:39</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>2026-07-20 13:27:50</t>
+          <t>2026-07-20 21:05:37</t>
         </is>
       </c>
       <c r="K600" t="b">
@@ -66856,28 +66856,28 @@
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>BSFP4473</t>
+          <t>BRTH5137</t>
         </is>
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="P600" t="n">
-        <v>5400</v>
+        <v>9200</v>
       </c>
       <c r="Q600" t="n">
-        <v>8000</v>
+        <v>10700</v>
       </c>
       <c r="R600" t="inlineStr">
         <is>
-          <t>Will King</t>
+          <t>David Ostendorf</t>
         </is>
       </c>
       <c r="S600" t="inlineStr">
@@ -66887,7 +66887,7 @@
       </c>
       <c r="T600" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
       <c r="U600" t="inlineStr">
@@ -66902,22 +66902,22 @@
       </c>
       <c r="W600" t="inlineStr">
         <is>
-          <t>6956994288</t>
+          <t>nwurayxntxfif89x</t>
         </is>
       </c>
       <c r="X600" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="Y600" t="inlineStr">
         <is>
-          <t>the plumber's plumber</t>
+          <t>Action Glass &amp; Mirror Inc</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>1216719974731854</t>
+          <t>1216730477297012</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -66932,7 +66932,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Jason Hockett</t>
+          <t>Will King</t>
         </is>
       </c>
       <c r="E601" t="inlineStr"/>
@@ -66943,18 +66943,18 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>2026-07-20 08:15:12</t>
+          <t>2026-07-20 12:30:59</t>
         </is>
       </c>
       <c r="H601" t="inlineStr"/>
       <c r="I601" t="inlineStr">
         <is>
-          <t>2026-07-20 13:26:38</t>
+          <t>2026-07-20 13:27:50</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>2026-07-20 13:26:38</t>
+          <t>2026-07-20 13:27:50</t>
         </is>
       </c>
       <c r="K601" t="b">
@@ -66967,28 +66967,28 @@
       </c>
       <c r="M601" t="inlineStr">
         <is>
-          <t>BCQF1440</t>
+          <t>BSFP4473</t>
         </is>
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="P601" t="n">
-        <v>3250</v>
+        <v>5400</v>
       </c>
       <c r="Q601" t="n">
-        <v>3750</v>
+        <v>8000</v>
       </c>
       <c r="R601" t="inlineStr">
         <is>
-          <t>Jason Hockett</t>
+          <t>Will King</t>
         </is>
       </c>
       <c r="S601" t="inlineStr">
@@ -67013,22 +67013,22 @@
       </c>
       <c r="W601" t="inlineStr">
         <is>
-          <t>hy1p2soruemodicq</t>
+          <t>6956994288</t>
         </is>
       </c>
       <c r="X601" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="Y601" t="inlineStr">
         <is>
-          <t>Greater Pitt Tree Service</t>
+          <t>the plumber's plumber</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>1216638001026912</t>
+          <t>1216719974731854</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -67043,33 +67043,29 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Summer Rima</t>
+          <t>Jason Hockett</t>
         </is>
       </c>
       <c r="E602" t="inlineStr"/>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>2026-07-16 09:09:35</t>
-        </is>
-      </c>
-      <c r="H602" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+          <t>2026-07-20 08:15:12</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr"/>
       <c r="I602" t="inlineStr">
         <is>
-          <t>2026-07-20 01:00:30</t>
+          <t>2026-07-20 13:26:38</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>2026-07-20 01:00:25</t>
+          <t>2026-07-20 13:26:38</t>
         </is>
       </c>
       <c r="K602" t="b">
@@ -67082,28 +67078,28 @@
       </c>
       <c r="M602" t="inlineStr">
         <is>
-          <t>BSDG2641</t>
+          <t>BCQF1440</t>
         </is>
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="P602" t="n">
-        <v>11100</v>
+        <v>3250</v>
       </c>
       <c r="Q602" t="n">
-        <v>13100</v>
+        <v>3750</v>
       </c>
       <c r="R602" t="inlineStr">
         <is>
-          <t>Summer Rima</t>
+          <t>Jason Hockett</t>
         </is>
       </c>
       <c r="S602" t="inlineStr">
@@ -67113,7 +67109,7 @@
       </c>
       <c r="T602" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U602" t="inlineStr">
@@ -67128,22 +67124,22 @@
       </c>
       <c r="W602" t="inlineStr">
         <is>
-          <t>ewhtpgcyc18ajv39</t>
+          <t>hy1p2soruemodicq</t>
         </is>
       </c>
       <c r="X602" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="Y602" t="inlineStr">
         <is>
-          <t>EXT Enhancements Roofing &amp; Siding LLC</t>
+          <t>Greater Pitt Tree Service</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>1216638107677105</t>
+          <t>1216638001026912</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -67158,7 +67154,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Glenys Rodriguez Gomez</t>
+          <t>Summer Rima</t>
         </is>
       </c>
       <c r="E603" t="inlineStr"/>
@@ -67169,7 +67165,7 @@
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>2026-07-16 10:43:55</t>
+          <t>2026-07-16 09:09:35</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
@@ -67179,12 +67175,12 @@
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>2026-07-20 00:36:29</t>
+          <t>2026-07-20 01:00:30</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>2026-07-20 00:36:26</t>
+          <t>2026-07-20 01:00:25</t>
         </is>
       </c>
       <c r="K603" t="b">
@@ -67197,59 +67193,174 @@
       </c>
       <c r="M603" t="inlineStr">
         <is>
+          <t>BSDG2641</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="P603" t="n">
+        <v>11100</v>
+      </c>
+      <c r="Q603" t="n">
+        <v>13100</v>
+      </c>
+      <c r="R603" t="inlineStr">
+        <is>
+          <t>Summer Rima</t>
+        </is>
+      </c>
+      <c r="S603" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T603" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U603" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V603" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W603" t="inlineStr">
+        <is>
+          <t>ewhtpgcyc18ajv39</t>
+        </is>
+      </c>
+      <c r="X603" t="n">
+        <v>150</v>
+      </c>
+      <c r="Y603" t="inlineStr">
+        <is>
+          <t>EXT Enhancements Roofing &amp; Siding LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>1216638107677105</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Glenys Rodriguez Gomez</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr"/>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Dexter Tardy</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:43:55</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>2026-07-20 00:36:29</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>2026-07-20 00:36:26</t>
+        </is>
+      </c>
+      <c r="K604" t="b">
+        <v>1</v>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
           <t xml:space="preserve"> BBJF0221</t>
         </is>
       </c>
-      <c r="N603" t="inlineStr">
+      <c r="N604" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="O603" t="inlineStr">
+      <c r="O604" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="P603" t="n">
+      <c r="P604" t="n">
         <v>250</v>
       </c>
-      <c r="Q603" t="n">
+      <c r="Q604" t="n">
         <v>400</v>
       </c>
-      <c r="R603" t="inlineStr">
+      <c r="R604" t="inlineStr">
         <is>
           <t>Glenys Rodriguez Gomez</t>
         </is>
       </c>
-      <c r="S603" t="inlineStr">
+      <c r="S604" t="inlineStr">
         <is>
           <t>Reoccurring Charge</t>
         </is>
       </c>
-      <c r="T603" t="inlineStr">
+      <c r="T604" t="inlineStr">
         <is>
           <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
-      <c r="U603" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V603" t="inlineStr">
+      <c r="U604" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V604" t="inlineStr">
         <is>
           <t>CER was closed already</t>
         </is>
       </c>
-      <c r="W603" t="inlineStr">
+      <c r="W604" t="inlineStr">
         <is>
           <t>CC_1C03CA819</t>
         </is>
       </c>
-      <c r="X603" t="n">
+      <c r="X604" t="n">
         <v>10</v>
       </c>
-      <c r="Y603" t="inlineStr">
+      <c r="Y604" t="inlineStr">
         <is>
           <t>Pizza And Stuff</t>
         </is>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y604"/>
+  <dimension ref="A1:Y610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66465,7 +66465,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>1216739682296057</t>
+          <t>1216728742070253</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -66480,29 +66480,33 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Mansi Aggarwal</t>
+          <t>Taylor Sloan</t>
         </is>
       </c>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Julian Komimbin</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>2026-07-20 21:13:35</t>
-        </is>
-      </c>
-      <c r="H597" t="inlineStr"/>
+          <t>2026-07-20 11:41:38</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>2026-07-21 17:25:43</t>
+          <t>2026-07-22 21:03:14</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>2026-07-21 17:25:18</t>
+          <t>2026-07-22 21:03:11</t>
         </is>
       </c>
       <c r="K597" t="b">
@@ -66510,33 +66514,33 @@
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>SaaS Add-On</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M597" t="inlineStr">
         <is>
-          <t>BSGC2255</t>
+          <t>BRXF8435</t>
         </is>
       </c>
       <c r="N597" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="P597" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="Q597" t="n">
-        <v>150</v>
+        <v>3500</v>
       </c>
       <c r="R597" t="inlineStr">
         <is>
-          <t>Mansi Aggarwal</t>
+          <t>Taylor Sloan</t>
         </is>
       </c>
       <c r="S597" t="inlineStr">
@@ -66546,7 +66550,7 @@
       </c>
       <c r="T597" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
       <c r="U597" t="inlineStr">
@@ -66556,27 +66560,27 @@
       </c>
       <c r="V597" t="inlineStr">
         <is>
-          <t>CER Still In Progress</t>
+          <t>CER was closed already</t>
         </is>
       </c>
       <c r="W597" t="inlineStr">
         <is>
-          <t>LOC162FA8667</t>
+          <t>bn06kt84woog63bo</t>
         </is>
       </c>
       <c r="X597" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="Y597" t="inlineStr">
         <is>
-          <t>TTW tilers trade warehouse</t>
+          <t>Low Price Auto Glass</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>1216672722760559</t>
+          <t>1216769215852730</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -66591,29 +66595,33 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Scott Jennings</t>
         </is>
       </c>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>2026-07-17 16:06:47</t>
-        </is>
-      </c>
-      <c r="H598" t="inlineStr"/>
+          <t>2026-07-21 14:54:55</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>2026-07-21 09:18:14</t>
+          <t>2026-07-22 16:48:13</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>2026-07-21 09:18:14</t>
+          <t>2026-07-22 16:48:11</t>
         </is>
       </c>
       <c r="K598" t="b">
@@ -66621,33 +66629,33 @@
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t>New Thryv Social Ads</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>BSCB8068</t>
+          <t>BRWQ3469</t>
         </is>
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P598" t="n">
-        <v>0</v>
+        <v>6250</v>
       </c>
       <c r="Q598" t="n">
-        <v>500</v>
+        <v>9250</v>
       </c>
       <c r="R598" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Scott Jennings</t>
         </is>
       </c>
       <c r="S598" t="inlineStr">
@@ -66657,7 +66665,7 @@
       </c>
       <c r="T598" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U598" t="inlineStr">
@@ -66667,27 +66675,27 @@
       </c>
       <c r="V598" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W598" t="inlineStr">
         <is>
-          <t>de846yo0m1x1y83t</t>
+          <t>Q3ND03P</t>
         </is>
       </c>
       <c r="X598" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="Y598" t="inlineStr">
         <is>
-          <t>Stroud Chiropractic PLLC</t>
+          <t>Vaccine Injury Lawyers</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>1216669020714116</t>
+          <t>1216772425817699</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -66702,33 +66710,33 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Madison McCaskey</t>
+          <t>Dominic Ondabu</t>
         </is>
       </c>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>2026-07-17 13:14:42</t>
+          <t>2026-07-21 17:54:21</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>2026-07-20 21:08:53</t>
+          <t>2026-07-22 16:45:24</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>2026-07-20 21:08:51</t>
+          <t>2026-07-22 16:45:22</t>
         </is>
       </c>
       <c r="K599" t="b">
@@ -66736,33 +66744,33 @@
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>SEO Increase</t>
         </is>
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>BRWJ6635</t>
+          <t>BFLH4868</t>
         </is>
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="P599" t="n">
-        <v>5200</v>
+        <v>1100</v>
       </c>
       <c r="Q599" t="n">
-        <v>6700</v>
+        <v>1500</v>
       </c>
       <c r="R599" t="inlineStr">
         <is>
-          <t>Madison McCaskey</t>
+          <t>Dominic Ondabu</t>
         </is>
       </c>
       <c r="S599" t="inlineStr">
@@ -66772,7 +66780,7 @@
       </c>
       <c r="T599" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U599" t="inlineStr">
@@ -66787,22 +66795,22 @@
       </c>
       <c r="W599" t="inlineStr">
         <is>
-          <t>awtjpp33s3vhq5t2</t>
+          <t>jhu5xzfqdmkx7zfr</t>
         </is>
       </c>
       <c r="X599" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="Y599" t="inlineStr">
         <is>
-          <t>Boone Heating &amp; Air Conditioning Inc</t>
+          <t>Law Office of Carlos Molinar</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>1216720207491318</t>
+          <t>1216789986150810</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -66817,33 +66825,29 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>David Ostendorf</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>2026-07-20 08:18:44</t>
-        </is>
-      </c>
-      <c r="H600" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+          <t>2026-07-22 08:59:21</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr"/>
       <c r="I600" t="inlineStr">
         <is>
-          <t>2026-07-20 21:05:39</t>
+          <t>2026-07-22 13:06:11</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>2026-07-20 21:05:37</t>
+          <t>2026-07-22 13:06:11</t>
         </is>
       </c>
       <c r="K600" t="b">
@@ -66856,28 +66860,28 @@
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>BRTH5137</t>
+          <t>BRXF0778</t>
         </is>
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P600" t="n">
-        <v>9200</v>
+        <v>7000</v>
       </c>
       <c r="Q600" t="n">
-        <v>10700</v>
+        <v>8000</v>
       </c>
       <c r="R600" t="inlineStr">
         <is>
-          <t>David Ostendorf</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="S600" t="inlineStr">
@@ -66887,7 +66891,7 @@
       </c>
       <c r="T600" t="inlineStr">
         <is>
-          <t>Recommendation sent via email and closed by BA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U600" t="inlineStr">
@@ -66902,7 +66906,7 @@
       </c>
       <c r="W600" t="inlineStr">
         <is>
-          <t>nwurayxntxfif89x</t>
+          <t>80i4envpy4li3wu7</t>
         </is>
       </c>
       <c r="X600" t="n">
@@ -66910,14 +66914,14 @@
       </c>
       <c r="Y600" t="inlineStr">
         <is>
-          <t>Action Glass &amp; Mirror Inc</t>
+          <t>H&amp;H Plumbing Contractors</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>1216730477297012</t>
+          <t>1216761973595601</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -66932,29 +66936,33 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Will King</t>
+          <t>Staci Maples</t>
         </is>
       </c>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Carla Miner-Luginbyhl</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>2026-07-20 12:30:59</t>
-        </is>
-      </c>
-      <c r="H601" t="inlineStr"/>
+          <t>2026-07-21 10:54:06</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>2026-07-20 13:27:50</t>
+          <t>2026-07-22 12:04:27</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>2026-07-20 13:27:50</t>
+          <t>2026-07-22 12:04:24</t>
         </is>
       </c>
       <c r="K601" t="b">
@@ -66967,35 +66975,27 @@
       </c>
       <c r="M601" t="inlineStr">
         <is>
-          <t>BSFP4473</t>
+          <t>BSFZ1940</t>
         </is>
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="P601" t="n">
-        <v>5400</v>
-      </c>
-      <c r="Q601" t="n">
-        <v>8000</v>
-      </c>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P601" t="inlineStr"/>
+      <c r="Q601" t="inlineStr"/>
       <c r="R601" t="inlineStr">
         <is>
-          <t>Will King</t>
-        </is>
-      </c>
-      <c r="S601" t="inlineStr">
-        <is>
-          <t>Reoccurring Charge</t>
-        </is>
-      </c>
+          <t>Staci Maples</t>
+        </is>
+      </c>
+      <c r="S601" t="inlineStr"/>
       <c r="T601" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -67013,22 +67013,20 @@
       </c>
       <c r="W601" t="inlineStr">
         <is>
-          <t>6956994288</t>
-        </is>
-      </c>
-      <c r="X601" t="n">
-        <v>150</v>
-      </c>
+          <t>LOCE5E4814B</t>
+        </is>
+      </c>
+      <c r="X601" t="inlineStr"/>
       <c r="Y601" t="inlineStr">
         <is>
-          <t>the plumber's plumber</t>
+          <t>Nature Tree Service</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>1216719974731854</t>
+          <t>1216251694736989</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -67043,29 +67041,33 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Jason Hockett</t>
+          <t>Antonio Perez</t>
         </is>
       </c>
       <c r="E602" t="inlineStr"/>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Carla Miner-Luginbyhl</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>2026-07-20 08:15:12</t>
-        </is>
-      </c>
-      <c r="H602" t="inlineStr"/>
+          <t>2026-07-02 15:53:18</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>2026-07-20 13:26:38</t>
+          <t>2026-07-22 11:56:55</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>2026-07-20 13:26:38</t>
+          <t>2026-07-22 11:56:04</t>
         </is>
       </c>
       <c r="K602" t="b">
@@ -67073,33 +67075,33 @@
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>New SEO</t>
         </is>
       </c>
       <c r="M602" t="inlineStr">
         <is>
-          <t>BCQF1440</t>
+          <t>BRXH9480</t>
         </is>
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P602" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="Q602" t="n">
-        <v>3750</v>
+        <v>2700</v>
       </c>
       <c r="R602" t="inlineStr">
         <is>
-          <t>Jason Hockett</t>
+          <t>Antonio Perez</t>
         </is>
       </c>
       <c r="S602" t="inlineStr">
@@ -67119,27 +67121,25 @@
       </c>
       <c r="V602" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W602" t="inlineStr">
         <is>
-          <t>hy1p2soruemodicq</t>
-        </is>
-      </c>
-      <c r="X602" t="n">
-        <v>25</v>
-      </c>
+          <t>LOCDAD72547</t>
+        </is>
+      </c>
+      <c r="X602" t="inlineStr"/>
       <c r="Y602" t="inlineStr">
         <is>
-          <t>Greater Pitt Tree Service</t>
+          <t>Ernies Plumbing &amp; Sewer Service</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>1216638001026912</t>
+          <t>1216739682296057</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -67154,33 +67154,29 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Summer Rima</t>
+          <t>Mansi Aggarwal</t>
         </is>
       </c>
       <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Julian Komimbin</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>2026-07-16 09:09:35</t>
-        </is>
-      </c>
-      <c r="H603" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+          <t>2026-07-20 21:13:35</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr"/>
       <c r="I603" t="inlineStr">
         <is>
-          <t>2026-07-20 01:00:30</t>
+          <t>2026-07-21 17:25:43</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>2026-07-20 01:00:25</t>
+          <t>2026-07-21 17:25:18</t>
         </is>
       </c>
       <c r="K603" t="b">
@@ -67188,33 +67184,33 @@
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>SaaS Add-On</t>
         </is>
       </c>
       <c r="M603" t="inlineStr">
         <is>
-          <t>BSDG2641</t>
+          <t>BSGC2255</t>
         </is>
       </c>
       <c r="N603" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="P603" t="n">
-        <v>11100</v>
+        <v>0</v>
       </c>
       <c r="Q603" t="n">
-        <v>13100</v>
+        <v>150</v>
       </c>
       <c r="R603" t="inlineStr">
         <is>
-          <t>Summer Rima</t>
+          <t>Mansi Aggarwal</t>
         </is>
       </c>
       <c r="S603" t="inlineStr">
@@ -67224,7 +67220,7 @@
       </c>
       <c r="T603" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U603" t="inlineStr">
@@ -67234,27 +67230,27 @@
       </c>
       <c r="V603" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W603" t="inlineStr">
         <is>
-          <t>ewhtpgcyc18ajv39</t>
+          <t>LOC162FA8667</t>
         </is>
       </c>
       <c r="X603" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="Y603" t="inlineStr">
         <is>
-          <t>EXT Enhancements Roofing &amp; Siding LLC</t>
+          <t>TTW tilers trade warehouse</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>1216638107677105</t>
+          <t>1216672722760559</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -67269,33 +67265,29 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Glenys Rodriguez Gomez</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="E604" t="inlineStr"/>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>2026-07-16 10:43:55</t>
-        </is>
-      </c>
-      <c r="H604" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+          <t>2026-07-17 16:06:47</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr"/>
       <c r="I604" t="inlineStr">
         <is>
-          <t>2026-07-20 00:36:29</t>
+          <t>2026-07-21 09:18:14</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>2026-07-20 00:36:26</t>
+          <t>2026-07-21 09:18:14</t>
         </is>
       </c>
       <c r="K604" t="b">
@@ -67303,64 +67295,746 @@
       </c>
       <c r="L604" t="inlineStr">
         <is>
+          <t>New Thryv Social Ads</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>BSCB8068</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="P604" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q604" t="n">
+        <v>500</v>
+      </c>
+      <c r="R604" t="inlineStr">
+        <is>
+          <t>La'Donna Williams</t>
+        </is>
+      </c>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T604" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U604" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V604" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W604" t="inlineStr">
+        <is>
+          <t>de846yo0m1x1y83t</t>
+        </is>
+      </c>
+      <c r="X604" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y604" t="inlineStr">
+        <is>
+          <t>Stroud Chiropractic PLLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>1216669020714116</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Madison McCaskey</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr"/>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Dexter Tardy</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>2026-07-17 13:14:42</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:08:53</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:08:51</t>
+        </is>
+      </c>
+      <c r="K605" t="b">
+        <v>1</v>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
           <t>TL Increase</t>
         </is>
       </c>
-      <c r="M604" t="inlineStr">
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>BRWJ6635</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="P605" t="n">
+        <v>5200</v>
+      </c>
+      <c r="Q605" t="n">
+        <v>6700</v>
+      </c>
+      <c r="R605" t="inlineStr">
+        <is>
+          <t>Madison McCaskey</t>
+        </is>
+      </c>
+      <c r="S605" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T605" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U605" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V605" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W605" t="inlineStr">
+        <is>
+          <t>awtjpp33s3vhq5t2</t>
+        </is>
+      </c>
+      <c r="X605" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y605" t="inlineStr">
+        <is>
+          <t>Boone Heating &amp; Air Conditioning Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>1216720207491318</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>David Ostendorf</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr"/>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Dexter Tardy</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:18:44</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:05:39</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:05:37</t>
+        </is>
+      </c>
+      <c r="K606" t="b">
+        <v>1</v>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>BRTH5137</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="P606" t="n">
+        <v>9200</v>
+      </c>
+      <c r="Q606" t="n">
+        <v>10700</v>
+      </c>
+      <c r="R606" t="inlineStr">
+        <is>
+          <t>David Ostendorf</t>
+        </is>
+      </c>
+      <c r="S606" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T606" t="inlineStr">
+        <is>
+          <t>Recommendation sent via email and closed by BA</t>
+        </is>
+      </c>
+      <c r="U606" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V606" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W606" t="inlineStr">
+        <is>
+          <t>nwurayxntxfif89x</t>
+        </is>
+      </c>
+      <c r="X606" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y606" t="inlineStr">
+        <is>
+          <t>Action Glass &amp; Mirror Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>1216730477297012</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Will King</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr"/>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Julia Cowden</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:30:59</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr"/>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:27:50</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:27:50</t>
+        </is>
+      </c>
+      <c r="K607" t="b">
+        <v>1</v>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>BSFP4473</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="P607" t="n">
+        <v>5400</v>
+      </c>
+      <c r="Q607" t="n">
+        <v>8000</v>
+      </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>Will King</t>
+        </is>
+      </c>
+      <c r="S607" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T607" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U607" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V607" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W607" t="inlineStr">
+        <is>
+          <t>6956994288</t>
+        </is>
+      </c>
+      <c r="X607" t="n">
+        <v>150</v>
+      </c>
+      <c r="Y607" t="inlineStr">
+        <is>
+          <t>the plumber's plumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>1216719974731854</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Jason Hockett</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr"/>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Julia Cowden</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:15:12</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr"/>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:26:38</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:26:38</t>
+        </is>
+      </c>
+      <c r="K608" t="b">
+        <v>1</v>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>BCQF1440</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="P608" t="n">
+        <v>3250</v>
+      </c>
+      <c r="Q608" t="n">
+        <v>3750</v>
+      </c>
+      <c r="R608" t="inlineStr">
+        <is>
+          <t>Jason Hockett</t>
+        </is>
+      </c>
+      <c r="S608" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T608" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U608" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V608" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W608" t="inlineStr">
+        <is>
+          <t>hy1p2soruemodicq</t>
+        </is>
+      </c>
+      <c r="X608" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y608" t="inlineStr">
+        <is>
+          <t>Greater Pitt Tree Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>1216638001026912</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Summer Rima</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr"/>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Dexter Tardy</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>2026-07-16 09:09:35</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>2026-07-20 01:00:30</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>2026-07-20 01:00:25</t>
+        </is>
+      </c>
+      <c r="K609" t="b">
+        <v>1</v>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>BSDG2641</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="P609" t="n">
+        <v>11100</v>
+      </c>
+      <c r="Q609" t="n">
+        <v>13100</v>
+      </c>
+      <c r="R609" t="inlineStr">
+        <is>
+          <t>Summer Rima</t>
+        </is>
+      </c>
+      <c r="S609" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T609" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U609" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V609" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W609" t="inlineStr">
+        <is>
+          <t>ewhtpgcyc18ajv39</t>
+        </is>
+      </c>
+      <c r="X609" t="n">
+        <v>150</v>
+      </c>
+      <c r="Y609" t="inlineStr">
+        <is>
+          <t>EXT Enhancements Roofing &amp; Siding LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>1216638107677105</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Glenys Rodriguez Gomez</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr"/>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Dexter Tardy</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:43:55</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>2026-07-20 00:36:29</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>2026-07-20 00:36:26</t>
+        </is>
+      </c>
+      <c r="K610" t="b">
+        <v>1</v>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
         <is>
           <t xml:space="preserve"> BBJF0221</t>
         </is>
       </c>
-      <c r="N604" t="inlineStr">
+      <c r="N610" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="O604" t="inlineStr">
+      <c r="O610" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="P604" t="n">
+      <c r="P610" t="n">
         <v>250</v>
       </c>
-      <c r="Q604" t="n">
+      <c r="Q610" t="n">
         <v>400</v>
       </c>
-      <c r="R604" t="inlineStr">
+      <c r="R610" t="inlineStr">
         <is>
           <t>Glenys Rodriguez Gomez</t>
         </is>
       </c>
-      <c r="S604" t="inlineStr">
+      <c r="S610" t="inlineStr">
         <is>
           <t>Reoccurring Charge</t>
         </is>
       </c>
-      <c r="T604" t="inlineStr">
+      <c r="T610" t="inlineStr">
         <is>
           <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
-      <c r="U604" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V604" t="inlineStr">
+      <c r="U610" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V610" t="inlineStr">
         <is>
           <t>CER was closed already</t>
         </is>
       </c>
-      <c r="W604" t="inlineStr">
+      <c r="W610" t="inlineStr">
         <is>
           <t>CC_1C03CA819</t>
         </is>
       </c>
-      <c r="X604" t="n">
+      <c r="X610" t="n">
         <v>10</v>
       </c>
-      <c r="Y604" t="inlineStr">
+      <c r="Y610" t="inlineStr">
         <is>
           <t>Pizza And Stuff</t>
         </is>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y610"/>
+  <dimension ref="A1:Y612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66465,7 +66465,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>1216728742070253</t>
+          <t>1216817593298502</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -66480,7 +66480,7 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Taylor Sloan</t>
+          <t>Chyna Elias</t>
         </is>
       </c>
       <c r="E597" t="inlineStr"/>
@@ -66491,22 +66491,18 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>2026-07-20 11:41:38</t>
-        </is>
-      </c>
-      <c r="H597" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
+          <t>2026-07-22 14:04:48</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr"/>
       <c r="I597" t="inlineStr">
         <is>
-          <t>2026-07-22 21:03:14</t>
+          <t>2026-07-23 09:37:25</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>2026-07-22 21:03:11</t>
+          <t>2026-07-23 09:37:23</t>
         </is>
       </c>
       <c r="K597" t="b">
@@ -66514,33 +66510,33 @@
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>New MC</t>
         </is>
       </c>
       <c r="M597" t="inlineStr">
         <is>
-          <t>BRXF8435</t>
+          <t>BSCJ7580</t>
         </is>
       </c>
       <c r="N597" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="P597" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="Q597" t="n">
-        <v>3500</v>
+        <v>255</v>
       </c>
       <c r="R597" t="inlineStr">
         <is>
-          <t>Taylor Sloan</t>
+          <t>Chyna Elias</t>
         </is>
       </c>
       <c r="S597" t="inlineStr">
@@ -66550,7 +66546,7 @@
       </c>
       <c r="T597" t="inlineStr">
         <is>
-          <t>Recommendation sent via email and closed by BA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U597" t="inlineStr">
@@ -66565,22 +66561,22 @@
       </c>
       <c r="W597" t="inlineStr">
         <is>
-          <t>bn06kt84woog63bo</t>
+          <t>Wv16qg0616cl6jwp</t>
         </is>
       </c>
       <c r="X597" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y597" t="inlineStr">
         <is>
-          <t>Low Price Auto Glass</t>
+          <t>Republic of Texas Concrete Coatings</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>1216769215852730</t>
+          <t>1216662060845690</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -66595,7 +66591,7 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Scott Jennings</t>
+          <t>Lauren Crutchfield</t>
         </is>
       </c>
       <c r="E598" t="inlineStr"/>
@@ -66606,7 +66602,7 @@
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>2026-07-21 14:54:55</t>
+          <t>2026-07-17 09:39:28</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -66616,12 +66612,12 @@
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>2026-07-22 16:48:13</t>
+          <t>2026-07-23 09:36:08</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>2026-07-22 16:48:11</t>
+          <t>2026-07-23 09:36:06</t>
         </is>
       </c>
       <c r="K598" t="b">
@@ -66634,28 +66630,28 @@
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>BRWQ3469</t>
+          <t>BCKG2302</t>
         </is>
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="P598" t="n">
-        <v>6250</v>
+        <v>1800</v>
       </c>
       <c r="Q598" t="n">
-        <v>9250</v>
+        <v>2300</v>
       </c>
       <c r="R598" t="inlineStr">
         <is>
-          <t>Scott Jennings</t>
+          <t>Lauren Crutchfield</t>
         </is>
       </c>
       <c r="S598" t="inlineStr">
@@ -66680,22 +66676,22 @@
       </c>
       <c r="W598" t="inlineStr">
         <is>
-          <t>Q3ND03P</t>
+          <t>cifelhaaqpmnt6s2</t>
         </is>
       </c>
       <c r="X598" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="Y598" t="inlineStr">
         <is>
-          <t>Vaccine Injury Lawyers</t>
+          <t>The Law Offices of Paul S Missan</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>1216772425817699</t>
+          <t>1216728742070253</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -66710,7 +66706,7 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Dominic Ondabu</t>
+          <t>Taylor Sloan</t>
         </is>
       </c>
       <c r="E599" t="inlineStr"/>
@@ -66721,7 +66717,7 @@
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>2026-07-21 17:54:21</t>
+          <t>2026-07-20 11:41:38</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -66731,12 +66727,12 @@
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>2026-07-22 16:45:24</t>
+          <t>2026-07-22 21:03:14</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>2026-07-22 16:45:22</t>
+          <t>2026-07-22 21:03:11</t>
         </is>
       </c>
       <c r="K599" t="b">
@@ -66744,33 +66740,33 @@
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>SEO Increase</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>BFLH4868</t>
+          <t>BRXF8435</t>
         </is>
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="P599" t="n">
-        <v>1100</v>
+        <v>2500</v>
       </c>
       <c r="Q599" t="n">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="R599" t="inlineStr">
         <is>
-          <t>Dominic Ondabu</t>
+          <t>Taylor Sloan</t>
         </is>
       </c>
       <c r="S599" t="inlineStr">
@@ -66780,7 +66776,7 @@
       </c>
       <c r="T599" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
       <c r="U599" t="inlineStr">
@@ -66795,22 +66791,22 @@
       </c>
       <c r="W599" t="inlineStr">
         <is>
-          <t>jhu5xzfqdmkx7zfr</t>
+          <t>bn06kt84woog63bo</t>
         </is>
       </c>
       <c r="X599" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="Y599" t="inlineStr">
         <is>
-          <t>Law Office of Carlos Molinar</t>
+          <t>Low Price Auto Glass</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>1216789986150810</t>
+          <t>1216769215852730</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -66825,29 +66821,33 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Scott Jennings</t>
         </is>
       </c>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>2026-07-22 08:59:21</t>
-        </is>
-      </c>
-      <c r="H600" t="inlineStr"/>
+          <t>2026-07-21 14:54:55</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>2026-07-22 13:06:11</t>
+          <t>2026-07-22 16:48:13</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>2026-07-22 13:06:11</t>
+          <t>2026-07-22 16:48:11</t>
         </is>
       </c>
       <c r="K600" t="b">
@@ -66860,28 +66860,28 @@
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>BRXF0778</t>
+          <t>BRWQ3469</t>
         </is>
       </c>
       <c r="N600" t="inlineStr">
         <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="O600" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
       <c r="P600" t="n">
-        <v>7000</v>
+        <v>6250</v>
       </c>
       <c r="Q600" t="n">
-        <v>8000</v>
+        <v>9250</v>
       </c>
       <c r="R600" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Scott Jennings</t>
         </is>
       </c>
       <c r="S600" t="inlineStr">
@@ -66901,27 +66901,27 @@
       </c>
       <c r="V600" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W600" t="inlineStr">
         <is>
-          <t>80i4envpy4li3wu7</t>
+          <t>Q3ND03P</t>
         </is>
       </c>
       <c r="X600" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="Y600" t="inlineStr">
         <is>
-          <t>H&amp;H Plumbing Contractors</t>
+          <t>Vaccine Injury Lawyers</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>1216761973595601</t>
+          <t>1216772425817699</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -66936,33 +66936,33 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Staci Maples</t>
+          <t>Dominic Ondabu</t>
         </is>
       </c>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Carla Miner-Luginbyhl</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>2026-07-21 10:54:06</t>
+          <t>2026-07-21 17:54:21</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>2026-07-22 12:04:27</t>
+          <t>2026-07-22 16:45:24</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>2026-07-22 12:04:24</t>
+          <t>2026-07-22 16:45:22</t>
         </is>
       </c>
       <c r="K601" t="b">
@@ -66970,32 +66970,40 @@
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>SEO Increase</t>
         </is>
       </c>
       <c r="M601" t="inlineStr">
         <is>
-          <t>BSFZ1940</t>
+          <t>BFLH4868</t>
         </is>
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="P601" t="inlineStr"/>
-      <c r="Q601" t="inlineStr"/>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="P601" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q601" t="n">
+        <v>1500</v>
+      </c>
       <c r="R601" t="inlineStr">
         <is>
-          <t>Staci Maples</t>
-        </is>
-      </c>
-      <c r="S601" t="inlineStr"/>
+          <t>Dominic Ondabu</t>
+        </is>
+      </c>
+      <c r="S601" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
       <c r="T601" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -67013,20 +67021,22 @@
       </c>
       <c r="W601" t="inlineStr">
         <is>
-          <t>LOCE5E4814B</t>
-        </is>
-      </c>
-      <c r="X601" t="inlineStr"/>
+          <t>jhu5xzfqdmkx7zfr</t>
+        </is>
+      </c>
+      <c r="X601" t="n">
+        <v>25</v>
+      </c>
       <c r="Y601" t="inlineStr">
         <is>
-          <t>Nature Tree Service</t>
+          <t>Law Office of Carlos Molinar</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>1216251694736989</t>
+          <t>1216789986150810</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -67041,33 +67051,29 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Antonio Perez</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="E602" t="inlineStr"/>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Carla Miner-Luginbyhl</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>2026-07-02 15:53:18</t>
-        </is>
-      </c>
-      <c r="H602" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-07-22 08:59:21</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr"/>
       <c r="I602" t="inlineStr">
         <is>
-          <t>2026-07-22 11:56:55</t>
+          <t>2026-07-22 13:06:11</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>2026-07-22 11:56:04</t>
+          <t>2026-07-22 13:06:11</t>
         </is>
       </c>
       <c r="K602" t="b">
@@ -67075,33 +67081,33 @@
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>New SEO</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M602" t="inlineStr">
         <is>
-          <t>BRXH9480</t>
+          <t>BRXF0778</t>
         </is>
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P602" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="Q602" t="n">
-        <v>2700</v>
+        <v>8000</v>
       </c>
       <c r="R602" t="inlineStr">
         <is>
-          <t>Antonio Perez</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="S602" t="inlineStr">
@@ -67121,25 +67127,27 @@
       </c>
       <c r="V602" t="inlineStr">
         <is>
-          <t>CER Still In Progress</t>
+          <t>CER was closed already</t>
         </is>
       </c>
       <c r="W602" t="inlineStr">
         <is>
-          <t>LOCDAD72547</t>
-        </is>
-      </c>
-      <c r="X602" t="inlineStr"/>
+          <t>80i4envpy4li3wu7</t>
+        </is>
+      </c>
+      <c r="X602" t="n">
+        <v>100</v>
+      </c>
       <c r="Y602" t="inlineStr">
         <is>
-          <t>Ernies Plumbing &amp; Sewer Service</t>
+          <t>H&amp;H Plumbing Contractors</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>1216739682296057</t>
+          <t>1216761973595601</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -67154,29 +67162,33 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Mansi Aggarwal</t>
+          <t>Staci Maples</t>
         </is>
       </c>
       <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Julian Komimbin</t>
+          <t>Carla Miner-Luginbyhl</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>2026-07-20 21:13:35</t>
-        </is>
-      </c>
-      <c r="H603" t="inlineStr"/>
+          <t>2026-07-21 10:54:06</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>2026-07-21 17:25:43</t>
+          <t>2026-07-22 12:04:27</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>2026-07-21 17:25:18</t>
+          <t>2026-07-22 12:04:24</t>
         </is>
       </c>
       <c r="K603" t="b">
@@ -67184,12 +67196,12 @@
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t>SaaS Add-On</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M603" t="inlineStr">
         <is>
-          <t>BSGC2255</t>
+          <t>BSFZ1940</t>
         </is>
       </c>
       <c r="N603" t="inlineStr">
@@ -67199,25 +67211,17 @@
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="P603" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q603" t="n">
-        <v>150</v>
-      </c>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P603" t="inlineStr"/>
+      <c r="Q603" t="inlineStr"/>
       <c r="R603" t="inlineStr">
         <is>
-          <t>Mansi Aggarwal</t>
-        </is>
-      </c>
-      <c r="S603" t="inlineStr">
-        <is>
-          <t>Reoccurring Charge</t>
-        </is>
-      </c>
+          <t>Staci Maples</t>
+        </is>
+      </c>
+      <c r="S603" t="inlineStr"/>
       <c r="T603" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -67230,27 +67234,25 @@
       </c>
       <c r="V603" t="inlineStr">
         <is>
-          <t>CER Still In Progress</t>
+          <t>CER was closed already</t>
         </is>
       </c>
       <c r="W603" t="inlineStr">
         <is>
-          <t>LOC162FA8667</t>
-        </is>
-      </c>
-      <c r="X603" t="n">
-        <v>10</v>
-      </c>
+          <t>LOCE5E4814B</t>
+        </is>
+      </c>
+      <c r="X603" t="inlineStr"/>
       <c r="Y603" t="inlineStr">
         <is>
-          <t>TTW tilers trade warehouse</t>
+          <t>Nature Tree Service</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>1216672722760559</t>
+          <t>1216251694736989</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -67265,29 +67267,33 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Antonio Perez</t>
         </is>
       </c>
       <c r="E604" t="inlineStr"/>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Carla Miner-Luginbyhl</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>2026-07-17 16:06:47</t>
-        </is>
-      </c>
-      <c r="H604" t="inlineStr"/>
+          <t>2026-07-02 15:53:18</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>2026-07-21 09:18:14</t>
+          <t>2026-07-22 11:56:55</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>2026-07-21 09:18:14</t>
+          <t>2026-07-22 11:56:04</t>
         </is>
       </c>
       <c r="K604" t="b">
@@ -67295,33 +67301,33 @@
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>New Thryv Social Ads</t>
+          <t>New SEO</t>
         </is>
       </c>
       <c r="M604" t="inlineStr">
         <is>
-          <t>BSCB8068</t>
+          <t>BRXH9480</t>
         </is>
       </c>
       <c r="N604" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P604" t="n">
         <v>0</v>
       </c>
       <c r="Q604" t="n">
-        <v>500</v>
+        <v>2700</v>
       </c>
       <c r="R604" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Antonio Perez</t>
         </is>
       </c>
       <c r="S604" t="inlineStr">
@@ -67331,7 +67337,7 @@
       </c>
       <c r="T604" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U604" t="inlineStr">
@@ -67341,27 +67347,25 @@
       </c>
       <c r="V604" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W604" t="inlineStr">
         <is>
-          <t>de846yo0m1x1y83t</t>
-        </is>
-      </c>
-      <c r="X604" t="n">
-        <v>25</v>
-      </c>
+          <t>LOCDAD72547</t>
+        </is>
+      </c>
+      <c r="X604" t="inlineStr"/>
       <c r="Y604" t="inlineStr">
         <is>
-          <t>Stroud Chiropractic PLLC</t>
+          <t>Ernies Plumbing &amp; Sewer Service</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>1216669020714116</t>
+          <t>1216739682296057</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -67376,33 +67380,29 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Madison McCaskey</t>
+          <t>Mansi Aggarwal</t>
         </is>
       </c>
       <c r="E605" t="inlineStr"/>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Julian Komimbin</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>2026-07-17 13:14:42</t>
-        </is>
-      </c>
-      <c r="H605" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+          <t>2026-07-20 21:13:35</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr"/>
       <c r="I605" t="inlineStr">
         <is>
-          <t>2026-07-20 21:08:53</t>
+          <t>2026-07-21 17:25:43</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>2026-07-20 21:08:51</t>
+          <t>2026-07-21 17:25:18</t>
         </is>
       </c>
       <c r="K605" t="b">
@@ -67410,33 +67410,33 @@
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>SaaS Add-On</t>
         </is>
       </c>
       <c r="M605" t="inlineStr">
         <is>
-          <t>BRWJ6635</t>
+          <t>BSGC2255</t>
         </is>
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="P605" t="n">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="Q605" t="n">
-        <v>6700</v>
+        <v>150</v>
       </c>
       <c r="R605" t="inlineStr">
         <is>
-          <t>Madison McCaskey</t>
+          <t>Mansi Aggarwal</t>
         </is>
       </c>
       <c r="S605" t="inlineStr">
@@ -67446,7 +67446,7 @@
       </c>
       <c r="T605" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U605" t="inlineStr">
@@ -67456,27 +67456,27 @@
       </c>
       <c r="V605" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W605" t="inlineStr">
         <is>
-          <t>awtjpp33s3vhq5t2</t>
+          <t>LOC162FA8667</t>
         </is>
       </c>
       <c r="X605" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="Y605" t="inlineStr">
         <is>
-          <t>Boone Heating &amp; Air Conditioning Inc</t>
+          <t>TTW tilers trade warehouse</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>1216720207491318</t>
+          <t>1216672722760559</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -67491,33 +67491,29 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>David Ostendorf</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>2026-07-20 08:18:44</t>
-        </is>
-      </c>
-      <c r="H606" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+          <t>2026-07-17 16:06:47</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr"/>
       <c r="I606" t="inlineStr">
         <is>
-          <t>2026-07-20 21:05:39</t>
+          <t>2026-07-21 09:18:14</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>2026-07-20 21:05:37</t>
+          <t>2026-07-21 09:18:14</t>
         </is>
       </c>
       <c r="K606" t="b">
@@ -67525,33 +67521,33 @@
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>New Thryv Social Ads</t>
         </is>
       </c>
       <c r="M606" t="inlineStr">
         <is>
-          <t>BRTH5137</t>
+          <t>BSCB8068</t>
         </is>
       </c>
       <c r="N606" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="P606" t="n">
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="Q606" t="n">
-        <v>10700</v>
+        <v>500</v>
       </c>
       <c r="R606" t="inlineStr">
         <is>
-          <t>David Ostendorf</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="S606" t="inlineStr">
@@ -67561,7 +67557,7 @@
       </c>
       <c r="T606" t="inlineStr">
         <is>
-          <t>Recommendation sent via email and closed by BA</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U606" t="inlineStr">
@@ -67576,22 +67572,22 @@
       </c>
       <c r="W606" t="inlineStr">
         <is>
-          <t>nwurayxntxfif89x</t>
+          <t>de846yo0m1x1y83t</t>
         </is>
       </c>
       <c r="X606" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="Y606" t="inlineStr">
         <is>
-          <t>Action Glass &amp; Mirror Inc</t>
+          <t>Stroud Chiropractic PLLC</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>1216730477297012</t>
+          <t>1216669020714116</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -67606,29 +67602,33 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Will King</t>
+          <t>Madison McCaskey</t>
         </is>
       </c>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Dexter Tardy</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>2026-07-20 12:30:59</t>
-        </is>
-      </c>
-      <c r="H607" t="inlineStr"/>
+          <t>2026-07-17 13:14:42</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>2026-07-20 13:27:50</t>
+          <t>2026-07-20 21:08:53</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>2026-07-20 13:27:50</t>
+          <t>2026-07-20 21:08:51</t>
         </is>
       </c>
       <c r="K607" t="b">
@@ -67641,12 +67641,12 @@
       </c>
       <c r="M607" t="inlineStr">
         <is>
-          <t>BSFP4473</t>
+          <t>BRWJ6635</t>
         </is>
       </c>
       <c r="N607" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="O607" t="inlineStr">
@@ -67655,14 +67655,14 @@
         </is>
       </c>
       <c r="P607" t="n">
-        <v>5400</v>
+        <v>5200</v>
       </c>
       <c r="Q607" t="n">
-        <v>8000</v>
+        <v>6700</v>
       </c>
       <c r="R607" t="inlineStr">
         <is>
-          <t>Will King</t>
+          <t>Madison McCaskey</t>
         </is>
       </c>
       <c r="S607" t="inlineStr">
@@ -67672,7 +67672,7 @@
       </c>
       <c r="T607" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U607" t="inlineStr">
@@ -67687,22 +67687,22 @@
       </c>
       <c r="W607" t="inlineStr">
         <is>
-          <t>6956994288</t>
+          <t>awtjpp33s3vhq5t2</t>
         </is>
       </c>
       <c r="X607" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="Y607" t="inlineStr">
         <is>
-          <t>the plumber's plumber</t>
+          <t>Boone Heating &amp; Air Conditioning Inc</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>1216719974731854</t>
+          <t>1216720207491318</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -67717,29 +67717,33 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Jason Hockett</t>
+          <t>David Ostendorf</t>
         </is>
       </c>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Dexter Tardy</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>2026-07-20 08:15:12</t>
-        </is>
-      </c>
-      <c r="H608" t="inlineStr"/>
+          <t>2026-07-20 08:18:44</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>2026-07-20 13:26:38</t>
+          <t>2026-07-20 21:05:39</t>
         </is>
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>2026-07-20 13:26:38</t>
+          <t>2026-07-20 21:05:37</t>
         </is>
       </c>
       <c r="K608" t="b">
@@ -67752,28 +67756,28 @@
       </c>
       <c r="M608" t="inlineStr">
         <is>
-          <t>BCQF1440</t>
+          <t>BRTH5137</t>
         </is>
       </c>
       <c r="N608" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="O608" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="P608" t="n">
-        <v>3250</v>
+        <v>9200</v>
       </c>
       <c r="Q608" t="n">
-        <v>3750</v>
+        <v>10700</v>
       </c>
       <c r="R608" t="inlineStr">
         <is>
-          <t>Jason Hockett</t>
+          <t>David Ostendorf</t>
         </is>
       </c>
       <c r="S608" t="inlineStr">
@@ -67783,7 +67787,7 @@
       </c>
       <c r="T608" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
       <c r="U608" t="inlineStr">
@@ -67798,22 +67802,22 @@
       </c>
       <c r="W608" t="inlineStr">
         <is>
-          <t>hy1p2soruemodicq</t>
+          <t>nwurayxntxfif89x</t>
         </is>
       </c>
       <c r="X608" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="Y608" t="inlineStr">
         <is>
-          <t>Greater Pitt Tree Service</t>
+          <t>Action Glass &amp; Mirror Inc</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>1216638001026912</t>
+          <t>1216730477297012</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -67828,33 +67832,29 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Summer Rima</t>
+          <t>Will King</t>
         </is>
       </c>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>2026-07-16 09:09:35</t>
-        </is>
-      </c>
-      <c r="H609" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+          <t>2026-07-20 12:30:59</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr"/>
       <c r="I609" t="inlineStr">
         <is>
-          <t>2026-07-20 01:00:30</t>
+          <t>2026-07-20 13:27:50</t>
         </is>
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>2026-07-20 01:00:25</t>
+          <t>2026-07-20 13:27:50</t>
         </is>
       </c>
       <c r="K609" t="b">
@@ -67867,28 +67867,28 @@
       </c>
       <c r="M609" t="inlineStr">
         <is>
-          <t>BSDG2641</t>
+          <t>BSFP4473</t>
         </is>
       </c>
       <c r="N609" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="O609" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="P609" t="n">
-        <v>11100</v>
+        <v>5400</v>
       </c>
       <c r="Q609" t="n">
-        <v>13100</v>
+        <v>8000</v>
       </c>
       <c r="R609" t="inlineStr">
         <is>
-          <t>Summer Rima</t>
+          <t>Will King</t>
         </is>
       </c>
       <c r="S609" t="inlineStr">
@@ -67898,7 +67898,7 @@
       </c>
       <c r="T609" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U609" t="inlineStr">
@@ -67913,7 +67913,7 @@
       </c>
       <c r="W609" t="inlineStr">
         <is>
-          <t>ewhtpgcyc18ajv39</t>
+          <t>6956994288</t>
         </is>
       </c>
       <c r="X609" t="n">
@@ -67921,14 +67921,14 @@
       </c>
       <c r="Y609" t="inlineStr">
         <is>
-          <t>EXT Enhancements Roofing &amp; Siding LLC</t>
+          <t>the plumber's plumber</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>1216638107677105</t>
+          <t>1216719974731854</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -67943,33 +67943,29 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>Glenys Rodriguez Gomez</t>
+          <t>Jason Hockett</t>
         </is>
       </c>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>2026-07-16 10:43:55</t>
-        </is>
-      </c>
-      <c r="H610" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+          <t>2026-07-20 08:15:12</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr"/>
       <c r="I610" t="inlineStr">
         <is>
-          <t>2026-07-20 00:36:29</t>
+          <t>2026-07-20 13:26:38</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>2026-07-20 00:36:26</t>
+          <t>2026-07-20 13:26:38</t>
         </is>
       </c>
       <c r="K610" t="b">
@@ -67982,59 +67978,289 @@
       </c>
       <c r="M610" t="inlineStr">
         <is>
+          <t>BCQF1440</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="P610" t="n">
+        <v>3250</v>
+      </c>
+      <c r="Q610" t="n">
+        <v>3750</v>
+      </c>
+      <c r="R610" t="inlineStr">
+        <is>
+          <t>Jason Hockett</t>
+        </is>
+      </c>
+      <c r="S610" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T610" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U610" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V610" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W610" t="inlineStr">
+        <is>
+          <t>hy1p2soruemodicq</t>
+        </is>
+      </c>
+      <c r="X610" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y610" t="inlineStr">
+        <is>
+          <t>Greater Pitt Tree Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>1216638001026912</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Summer Rima</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr"/>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Dexter Tardy</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>2026-07-16 09:09:35</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>2026-07-20 01:00:30</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>2026-07-20 01:00:25</t>
+        </is>
+      </c>
+      <c r="K611" t="b">
+        <v>1</v>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>BSDG2641</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="P611" t="n">
+        <v>11100</v>
+      </c>
+      <c r="Q611" t="n">
+        <v>13100</v>
+      </c>
+      <c r="R611" t="inlineStr">
+        <is>
+          <t>Summer Rima</t>
+        </is>
+      </c>
+      <c r="S611" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T611" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U611" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V611" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W611" t="inlineStr">
+        <is>
+          <t>ewhtpgcyc18ajv39</t>
+        </is>
+      </c>
+      <c r="X611" t="n">
+        <v>150</v>
+      </c>
+      <c r="Y611" t="inlineStr">
+        <is>
+          <t>EXT Enhancements Roofing &amp; Siding LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>1216638107677105</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Glenys Rodriguez Gomez</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr"/>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Dexter Tardy</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:43:55</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>2026-07-20 00:36:29</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>2026-07-20 00:36:26</t>
+        </is>
+      </c>
+      <c r="K612" t="b">
+        <v>1</v>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
           <t xml:space="preserve"> BBJF0221</t>
         </is>
       </c>
-      <c r="N610" t="inlineStr">
+      <c r="N612" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="O610" t="inlineStr">
+      <c r="O612" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="P610" t="n">
+      <c r="P612" t="n">
         <v>250</v>
       </c>
-      <c r="Q610" t="n">
+      <c r="Q612" t="n">
         <v>400</v>
       </c>
-      <c r="R610" t="inlineStr">
+      <c r="R612" t="inlineStr">
         <is>
           <t>Glenys Rodriguez Gomez</t>
         </is>
       </c>
-      <c r="S610" t="inlineStr">
+      <c r="S612" t="inlineStr">
         <is>
           <t>Reoccurring Charge</t>
         </is>
       </c>
-      <c r="T610" t="inlineStr">
+      <c r="T612" t="inlineStr">
         <is>
           <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
-      <c r="U610" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V610" t="inlineStr">
+      <c r="U612" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V612" t="inlineStr">
         <is>
           <t>CER was closed already</t>
         </is>
       </c>
-      <c r="W610" t="inlineStr">
+      <c r="W612" t="inlineStr">
         <is>
           <t>CC_1C03CA819</t>
         </is>
       </c>
-      <c r="X610" t="n">
+      <c r="X612" t="n">
         <v>10</v>
       </c>
-      <c r="Y610" t="inlineStr">
+      <c r="Y612" t="inlineStr">
         <is>
           <t>Pizza And Stuff</t>
         </is>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y612"/>
+  <dimension ref="A1:Y616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66465,7 +66465,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>1216817593298502</t>
+          <t>1216859696731429</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -66480,29 +66480,29 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Chyna Elias</t>
+          <t>Yenifer Medina</t>
         </is>
       </c>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Shannon Comas</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>2026-07-22 14:04:48</t>
+          <t>2026-07-24 11:08:39</t>
         </is>
       </c>
       <c r="H597" t="inlineStr"/>
       <c r="I597" t="inlineStr">
         <is>
-          <t>2026-07-23 09:37:25</t>
+          <t>2026-07-24 14:44:38</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>2026-07-23 09:37:23</t>
+          <t>2026-07-24 14:44:38</t>
         </is>
       </c>
       <c r="K597" t="b">
@@ -66510,33 +66510,33 @@
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>New MC</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M597" t="inlineStr">
         <is>
-          <t>BSCJ7580</t>
+          <t>BLXJ4791</t>
         </is>
       </c>
       <c r="N597" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="P597" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Q597" t="n">
-        <v>255</v>
+        <v>3000</v>
       </c>
       <c r="R597" t="inlineStr">
         <is>
-          <t>Chyna Elias</t>
+          <t>Yenifer Medina</t>
         </is>
       </c>
       <c r="S597" t="inlineStr">
@@ -66546,7 +66546,7 @@
       </c>
       <c r="T597" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
       <c r="U597" t="inlineStr">
@@ -66561,22 +66561,22 @@
       </c>
       <c r="W597" t="inlineStr">
         <is>
-          <t>Wv16qg0616cl6jwp</t>
+          <t>h9l6iu2ukgo9mq0a</t>
         </is>
       </c>
       <c r="X597" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y597" t="inlineStr">
         <is>
-          <t>Republic of Texas Concrete Coatings</t>
+          <t>Marvs Quality Towing Service Inc</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>1216662060845690</t>
+          <t>1216834529911207</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -66591,33 +66591,29 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Lauren Crutchfield</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Shannon Comas</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>2026-07-17 09:39:28</t>
-        </is>
-      </c>
-      <c r="H598" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
+          <t>2026-07-23 13:11:33</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr"/>
       <c r="I598" t="inlineStr">
         <is>
-          <t>2026-07-23 09:36:08</t>
+          <t>2026-07-24 07:39:46</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>2026-07-23 09:36:06</t>
+          <t>2026-07-24 07:39:46</t>
         </is>
       </c>
       <c r="K598" t="b">
@@ -66630,28 +66626,28 @@
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>BCKG2302</t>
+          <t>BSCT8166</t>
         </is>
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="P598" t="n">
-        <v>1800</v>
+        <v>4700</v>
       </c>
       <c r="Q598" t="n">
-        <v>2300</v>
+        <v>7000</v>
       </c>
       <c r="R598" t="inlineStr">
         <is>
-          <t>Lauren Crutchfield</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="S598" t="inlineStr">
@@ -66661,7 +66657,7 @@
       </c>
       <c r="T598" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U598" t="inlineStr">
@@ -66671,27 +66667,27 @@
       </c>
       <c r="V598" t="inlineStr">
         <is>
-          <t>CER Still In Progress</t>
+          <t>CER was closed already</t>
         </is>
       </c>
       <c r="W598" t="inlineStr">
         <is>
-          <t>cifelhaaqpmnt6s2</t>
+          <t>LOC151D97BB3</t>
         </is>
       </c>
       <c r="X598" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="Y598" t="inlineStr">
         <is>
-          <t>The Law Offices of Paul S Missan</t>
+          <t>Kay's Affordable HVAC&amp;R</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>1216728742070253</t>
+          <t>1216840244857332</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -66706,33 +66702,29 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Taylor Sloan</t>
+          <t>Alicia Battiata</t>
         </is>
       </c>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Shannon Comas</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>2026-07-20 11:41:38</t>
-        </is>
-      </c>
-      <c r="H599" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
+          <t>2026-07-23 17:53:24</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr"/>
       <c r="I599" t="inlineStr">
         <is>
-          <t>2026-07-22 21:03:14</t>
+          <t>2026-07-24 07:38:43</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>2026-07-22 21:03:11</t>
+          <t>2026-07-24 07:38:39</t>
         </is>
       </c>
       <c r="K599" t="b">
@@ -66740,33 +66732,33 @@
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>New Thryv Social Ads</t>
         </is>
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>BRXF8435</t>
+          <t>BSFB4678</t>
         </is>
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="P599" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="Q599" t="n">
-        <v>3500</v>
+        <v>500</v>
       </c>
       <c r="R599" t="inlineStr">
         <is>
-          <t>Taylor Sloan</t>
+          <t>Alicia Battiata</t>
         </is>
       </c>
       <c r="S599" t="inlineStr">
@@ -66776,7 +66768,7 @@
       </c>
       <c r="T599" t="inlineStr">
         <is>
-          <t>Recommendation sent via email and closed by BA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U599" t="inlineStr">
@@ -66791,22 +66783,22 @@
       </c>
       <c r="W599" t="inlineStr">
         <is>
-          <t>bn06kt84woog63bo</t>
+          <t>cxoh9nldc0b9vi4n</t>
         </is>
       </c>
       <c r="X599" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="Y599" t="inlineStr">
         <is>
-          <t>Low Price Auto Glass</t>
+          <t>Vital Drip Lounge</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>1216769215852730</t>
+          <t>1216840107980282</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -66821,33 +66813,29 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Scott Jennings</t>
+          <t xml:space="preserve">Ruchi Sharma </t>
         </is>
       </c>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Shannon Comas</t>
+          <t>Julian Komimbin</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>2026-07-21 14:54:55</t>
-        </is>
-      </c>
-      <c r="H600" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
+          <t>2026-07-23 17:37:58</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr"/>
       <c r="I600" t="inlineStr">
         <is>
-          <t>2026-07-22 16:48:13</t>
+          <t>2026-07-24 04:08:13</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>2026-07-22 16:48:11</t>
+          <t>2026-07-24 04:08:04</t>
         </is>
       </c>
       <c r="K600" t="b">
@@ -66855,17 +66843,17 @@
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>New SEO</t>
         </is>
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>BRWQ3469</t>
+          <t>BSCZ5289</t>
         </is>
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="O600" t="inlineStr">
@@ -66874,14 +66862,14 @@
         </is>
       </c>
       <c r="P600" t="n">
-        <v>6250</v>
+        <v>0</v>
       </c>
       <c r="Q600" t="n">
-        <v>9250</v>
+        <v>875</v>
       </c>
       <c r="R600" t="inlineStr">
         <is>
-          <t>Scott Jennings</t>
+          <t xml:space="preserve">Ruchi Sharma </t>
         </is>
       </c>
       <c r="S600" t="inlineStr">
@@ -66891,7 +66879,7 @@
       </c>
       <c r="T600" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
       <c r="U600" t="inlineStr">
@@ -66906,22 +66894,22 @@
       </c>
       <c r="W600" t="inlineStr">
         <is>
-          <t>Q3ND03P</t>
+          <t>LOC119AABF3B</t>
         </is>
       </c>
       <c r="X600" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="Y600" t="inlineStr">
         <is>
-          <t>Vaccine Injury Lawyers</t>
+          <t>AARON JOHN BRADLEY</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>1216772425817699</t>
+          <t>1216817593298502</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -66936,7 +66924,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Dominic Ondabu</t>
+          <t>Chyna Elias</t>
         </is>
       </c>
       <c r="E601" t="inlineStr"/>
@@ -66947,22 +66935,18 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>2026-07-21 17:54:21</t>
-        </is>
-      </c>
-      <c r="H601" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
+          <t>2026-07-22 14:04:48</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr"/>
       <c r="I601" t="inlineStr">
         <is>
-          <t>2026-07-22 16:45:24</t>
+          <t>2026-07-23 09:37:25</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>2026-07-22 16:45:22</t>
+          <t>2026-07-23 09:37:23</t>
         </is>
       </c>
       <c r="K601" t="b">
@@ -66970,33 +66954,33 @@
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>SEO Increase</t>
+          <t>New MC</t>
         </is>
       </c>
       <c r="M601" t="inlineStr">
         <is>
-          <t>BFLH4868</t>
+          <t>BSCJ7580</t>
         </is>
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="P601" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="Q601" t="n">
-        <v>1500</v>
+        <v>255</v>
       </c>
       <c r="R601" t="inlineStr">
         <is>
-          <t>Dominic Ondabu</t>
+          <t>Chyna Elias</t>
         </is>
       </c>
       <c r="S601" t="inlineStr">
@@ -67021,22 +67005,22 @@
       </c>
       <c r="W601" t="inlineStr">
         <is>
-          <t>jhu5xzfqdmkx7zfr</t>
+          <t>Wv16qg0616cl6jwp</t>
         </is>
       </c>
       <c r="X601" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y601" t="inlineStr">
         <is>
-          <t>Law Office of Carlos Molinar</t>
+          <t>Republic of Texas Concrete Coatings</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>1216789986150810</t>
+          <t>1216662060845690</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -67051,29 +67035,33 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Lauren Crutchfield</t>
         </is>
       </c>
       <c r="E602" t="inlineStr"/>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>2026-07-22 08:59:21</t>
-        </is>
-      </c>
-      <c r="H602" t="inlineStr"/>
+          <t>2026-07-17 09:39:28</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>2026-07-22 13:06:11</t>
+          <t>2026-07-23 09:36:08</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>2026-07-22 13:06:11</t>
+          <t>2026-07-23 09:36:06</t>
         </is>
       </c>
       <c r="K602" t="b">
@@ -67086,28 +67074,28 @@
       </c>
       <c r="M602" t="inlineStr">
         <is>
-          <t>BRXF0778</t>
+          <t>BCKG2302</t>
         </is>
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="P602" t="n">
-        <v>7000</v>
+        <v>1800</v>
       </c>
       <c r="Q602" t="n">
-        <v>8000</v>
+        <v>2300</v>
       </c>
       <c r="R602" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Lauren Crutchfield</t>
         </is>
       </c>
       <c r="S602" t="inlineStr">
@@ -67127,27 +67115,27 @@
       </c>
       <c r="V602" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W602" t="inlineStr">
         <is>
-          <t>80i4envpy4li3wu7</t>
+          <t>cifelhaaqpmnt6s2</t>
         </is>
       </c>
       <c r="X602" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="Y602" t="inlineStr">
         <is>
-          <t>H&amp;H Plumbing Contractors</t>
+          <t>The Law Offices of Paul S Missan</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>1216761973595601</t>
+          <t>1216728742070253</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -67162,33 +67150,33 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Staci Maples</t>
+          <t>Taylor Sloan</t>
         </is>
       </c>
       <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Carla Miner-Luginbyhl</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>2026-07-21 10:54:06</t>
+          <t>2026-07-20 11:41:38</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>2026-07-22 12:04:27</t>
+          <t>2026-07-22 21:03:14</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>2026-07-22 12:04:24</t>
+          <t>2026-07-22 21:03:11</t>
         </is>
       </c>
       <c r="K603" t="b">
@@ -67201,12 +67189,12 @@
       </c>
       <c r="M603" t="inlineStr">
         <is>
-          <t>BSFZ1940</t>
+          <t>BRXF8435</t>
         </is>
       </c>
       <c r="N603" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="O603" t="inlineStr">
@@ -67214,17 +67202,25 @@
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P603" t="inlineStr"/>
-      <c r="Q603" t="inlineStr"/>
+      <c r="P603" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q603" t="n">
+        <v>3500</v>
+      </c>
       <c r="R603" t="inlineStr">
         <is>
-          <t>Staci Maples</t>
-        </is>
-      </c>
-      <c r="S603" t="inlineStr"/>
+          <t>Taylor Sloan</t>
+        </is>
+      </c>
+      <c r="S603" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
       <c r="T603" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
       <c r="U603" t="inlineStr">
@@ -67239,20 +67235,22 @@
       </c>
       <c r="W603" t="inlineStr">
         <is>
-          <t>LOCE5E4814B</t>
-        </is>
-      </c>
-      <c r="X603" t="inlineStr"/>
+          <t>bn06kt84woog63bo</t>
+        </is>
+      </c>
+      <c r="X603" t="n">
+        <v>100</v>
+      </c>
       <c r="Y603" t="inlineStr">
         <is>
-          <t>Nature Tree Service</t>
+          <t>Low Price Auto Glass</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>1216251694736989</t>
+          <t>1216769215852730</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -67267,33 +67265,33 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Antonio Perez</t>
+          <t>Scott Jennings</t>
         </is>
       </c>
       <c r="E604" t="inlineStr"/>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Carla Miner-Luginbyhl</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>2026-07-02 15:53:18</t>
+          <t>2026-07-21 14:54:55</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>2026-07-22 11:56:55</t>
+          <t>2026-07-22 16:48:13</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>2026-07-22 11:56:04</t>
+          <t>2026-07-22 16:48:11</t>
         </is>
       </c>
       <c r="K604" t="b">
@@ -67301,33 +67299,33 @@
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>New SEO</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M604" t="inlineStr">
         <is>
-          <t>BRXH9480</t>
+          <t>BRWQ3469</t>
         </is>
       </c>
       <c r="N604" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P604" t="n">
-        <v>0</v>
+        <v>6250</v>
       </c>
       <c r="Q604" t="n">
-        <v>2700</v>
+        <v>9250</v>
       </c>
       <c r="R604" t="inlineStr">
         <is>
-          <t>Antonio Perez</t>
+          <t>Scott Jennings</t>
         </is>
       </c>
       <c r="S604" t="inlineStr">
@@ -67352,20 +67350,22 @@
       </c>
       <c r="W604" t="inlineStr">
         <is>
-          <t>LOCDAD72547</t>
-        </is>
-      </c>
-      <c r="X604" t="inlineStr"/>
+          <t>Q3ND03P</t>
+        </is>
+      </c>
+      <c r="X604" t="n">
+        <v>150</v>
+      </c>
       <c r="Y604" t="inlineStr">
         <is>
-          <t>Ernies Plumbing &amp; Sewer Service</t>
+          <t>Vaccine Injury Lawyers</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>1216739682296057</t>
+          <t>1216772425817699</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -67380,29 +67380,33 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Mansi Aggarwal</t>
+          <t>Dominic Ondabu</t>
         </is>
       </c>
       <c r="E605" t="inlineStr"/>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Julian Komimbin</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>2026-07-20 21:13:35</t>
-        </is>
-      </c>
-      <c r="H605" t="inlineStr"/>
+          <t>2026-07-21 17:54:21</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>2026-07-21 17:25:43</t>
+          <t>2026-07-22 16:45:24</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>2026-07-21 17:25:18</t>
+          <t>2026-07-22 16:45:22</t>
         </is>
       </c>
       <c r="K605" t="b">
@@ -67410,33 +67414,33 @@
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>SaaS Add-On</t>
+          <t>SEO Increase</t>
         </is>
       </c>
       <c r="M605" t="inlineStr">
         <is>
-          <t>BSGC2255</t>
+          <t>BFLH4868</t>
         </is>
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="P605" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="Q605" t="n">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="R605" t="inlineStr">
         <is>
-          <t>Mansi Aggarwal</t>
+          <t>Dominic Ondabu</t>
         </is>
       </c>
       <c r="S605" t="inlineStr">
@@ -67456,27 +67460,27 @@
       </c>
       <c r="V605" t="inlineStr">
         <is>
-          <t>CER Still In Progress</t>
+          <t>CER was closed already</t>
         </is>
       </c>
       <c r="W605" t="inlineStr">
         <is>
-          <t>LOC162FA8667</t>
+          <t>jhu5xzfqdmkx7zfr</t>
         </is>
       </c>
       <c r="X605" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="Y605" t="inlineStr">
         <is>
-          <t>TTW tilers trade warehouse</t>
+          <t>Law Office of Carlos Molinar</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>1216672722760559</t>
+          <t>1216789986150810</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -67502,18 +67506,18 @@
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>2026-07-17 16:06:47</t>
+          <t>2026-07-22 08:59:21</t>
         </is>
       </c>
       <c r="H606" t="inlineStr"/>
       <c r="I606" t="inlineStr">
         <is>
-          <t>2026-07-21 09:18:14</t>
+          <t>2026-07-22 13:06:11</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>2026-07-21 09:18:14</t>
+          <t>2026-07-22 13:06:11</t>
         </is>
       </c>
       <c r="K606" t="b">
@@ -67521,29 +67525,29 @@
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>New Thryv Social Ads</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M606" t="inlineStr">
         <is>
-          <t>BSCB8068</t>
+          <t>BRXF0778</t>
         </is>
       </c>
       <c r="N606" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P606" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="Q606" t="n">
-        <v>500</v>
+        <v>8000</v>
       </c>
       <c r="R606" t="inlineStr">
         <is>
@@ -67557,7 +67561,7 @@
       </c>
       <c r="T606" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U606" t="inlineStr">
@@ -67572,22 +67576,22 @@
       </c>
       <c r="W606" t="inlineStr">
         <is>
-          <t>de846yo0m1x1y83t</t>
+          <t>80i4envpy4li3wu7</t>
         </is>
       </c>
       <c r="X606" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="Y606" t="inlineStr">
         <is>
-          <t>Stroud Chiropractic PLLC</t>
+          <t>H&amp;H Plumbing Contractors</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>1216669020714116</t>
+          <t>1216761973595601</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -67602,33 +67606,33 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Madison McCaskey</t>
+          <t>Staci Maples</t>
         </is>
       </c>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Carla Miner-Luginbyhl</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>2026-07-17 13:14:42</t>
+          <t>2026-07-21 10:54:06</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>2026-07-20 21:08:53</t>
+          <t>2026-07-22 12:04:27</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>2026-07-20 21:08:51</t>
+          <t>2026-07-22 12:04:24</t>
         </is>
       </c>
       <c r="K607" t="b">
@@ -67641,38 +67645,30 @@
       </c>
       <c r="M607" t="inlineStr">
         <is>
-          <t>BRWJ6635</t>
+          <t>BSFZ1940</t>
         </is>
       </c>
       <c r="N607" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O607" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="P607" t="n">
-        <v>5200</v>
-      </c>
-      <c r="Q607" t="n">
-        <v>6700</v>
-      </c>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P607" t="inlineStr"/>
+      <c r="Q607" t="inlineStr"/>
       <c r="R607" t="inlineStr">
         <is>
-          <t>Madison McCaskey</t>
-        </is>
-      </c>
-      <c r="S607" t="inlineStr">
-        <is>
-          <t>Reoccurring Charge</t>
-        </is>
-      </c>
+          <t>Staci Maples</t>
+        </is>
+      </c>
+      <c r="S607" t="inlineStr"/>
       <c r="T607" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U607" t="inlineStr">
@@ -67687,22 +67683,20 @@
       </c>
       <c r="W607" t="inlineStr">
         <is>
-          <t>awtjpp33s3vhq5t2</t>
-        </is>
-      </c>
-      <c r="X607" t="n">
-        <v>100</v>
-      </c>
+          <t>LOCE5E4814B</t>
+        </is>
+      </c>
+      <c r="X607" t="inlineStr"/>
       <c r="Y607" t="inlineStr">
         <is>
-          <t>Boone Heating &amp; Air Conditioning Inc</t>
+          <t>Nature Tree Service</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>1216720207491318</t>
+          <t>1216251694736989</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -67717,33 +67711,33 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>David Ostendorf</t>
+          <t>Antonio Perez</t>
         </is>
       </c>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Carla Miner-Luginbyhl</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>2026-07-20 08:18:44</t>
+          <t>2026-07-02 15:53:18</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>2026-07-20 21:05:39</t>
+          <t>2026-07-22 11:56:55</t>
         </is>
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>2026-07-20 21:05:37</t>
+          <t>2026-07-22 11:56:04</t>
         </is>
       </c>
       <c r="K608" t="b">
@@ -67751,33 +67745,33 @@
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>New SEO</t>
         </is>
       </c>
       <c r="M608" t="inlineStr">
         <is>
-          <t>BRTH5137</t>
+          <t>BRXH9480</t>
         </is>
       </c>
       <c r="N608" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="O608" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P608" t="n">
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="Q608" t="n">
-        <v>10700</v>
+        <v>2700</v>
       </c>
       <c r="R608" t="inlineStr">
         <is>
-          <t>David Ostendorf</t>
+          <t>Antonio Perez</t>
         </is>
       </c>
       <c r="S608" t="inlineStr">
@@ -67787,7 +67781,7 @@
       </c>
       <c r="T608" t="inlineStr">
         <is>
-          <t>Recommendation sent via email and closed by BA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U608" t="inlineStr">
@@ -67797,27 +67791,25 @@
       </c>
       <c r="V608" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W608" t="inlineStr">
         <is>
-          <t>nwurayxntxfif89x</t>
-        </is>
-      </c>
-      <c r="X608" t="n">
-        <v>100</v>
-      </c>
+          <t>LOCDAD72547</t>
+        </is>
+      </c>
+      <c r="X608" t="inlineStr"/>
       <c r="Y608" t="inlineStr">
         <is>
-          <t>Action Glass &amp; Mirror Inc</t>
+          <t>Ernies Plumbing &amp; Sewer Service</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>1216730477297012</t>
+          <t>1216739682296057</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -67832,29 +67824,29 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Will King</t>
+          <t>Mansi Aggarwal</t>
         </is>
       </c>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Julian Komimbin</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>2026-07-20 12:30:59</t>
+          <t>2026-07-20 21:13:35</t>
         </is>
       </c>
       <c r="H609" t="inlineStr"/>
       <c r="I609" t="inlineStr">
         <is>
-          <t>2026-07-20 13:27:50</t>
+          <t>2026-07-21 17:25:43</t>
         </is>
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>2026-07-20 13:27:50</t>
+          <t>2026-07-21 17:25:18</t>
         </is>
       </c>
       <c r="K609" t="b">
@@ -67862,33 +67854,33 @@
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>SaaS Add-On</t>
         </is>
       </c>
       <c r="M609" t="inlineStr">
         <is>
-          <t>BSFP4473</t>
+          <t>BSGC2255</t>
         </is>
       </c>
       <c r="N609" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O609" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="P609" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="Q609" t="n">
-        <v>8000</v>
+        <v>150</v>
       </c>
       <c r="R609" t="inlineStr">
         <is>
-          <t>Will King</t>
+          <t>Mansi Aggarwal</t>
         </is>
       </c>
       <c r="S609" t="inlineStr">
@@ -67908,27 +67900,27 @@
       </c>
       <c r="V609" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W609" t="inlineStr">
         <is>
-          <t>6956994288</t>
+          <t>LOC162FA8667</t>
         </is>
       </c>
       <c r="X609" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="Y609" t="inlineStr">
         <is>
-          <t>the plumber's plumber</t>
+          <t>TTW tilers trade warehouse</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>1216719974731854</t>
+          <t>1216672722760559</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -67943,7 +67935,7 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>Jason Hockett</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="E610" t="inlineStr"/>
@@ -67954,18 +67946,18 @@
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>2026-07-20 08:15:12</t>
+          <t>2026-07-17 16:06:47</t>
         </is>
       </c>
       <c r="H610" t="inlineStr"/>
       <c r="I610" t="inlineStr">
         <is>
-          <t>2026-07-20 13:26:38</t>
+          <t>2026-07-21 09:18:14</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>2026-07-20 13:26:38</t>
+          <t>2026-07-21 09:18:14</t>
         </is>
       </c>
       <c r="K610" t="b">
@@ -67973,33 +67965,33 @@
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>New Thryv Social Ads</t>
         </is>
       </c>
       <c r="M610" t="inlineStr">
         <is>
-          <t>BCQF1440</t>
+          <t>BSCB8068</t>
         </is>
       </c>
       <c r="N610" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="O610" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="P610" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="Q610" t="n">
-        <v>3750</v>
+        <v>500</v>
       </c>
       <c r="R610" t="inlineStr">
         <is>
-          <t>Jason Hockett</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="S610" t="inlineStr">
@@ -68009,7 +68001,7 @@
       </c>
       <c r="T610" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U610" t="inlineStr">
@@ -68024,7 +68016,7 @@
       </c>
       <c r="W610" t="inlineStr">
         <is>
-          <t>hy1p2soruemodicq</t>
+          <t>de846yo0m1x1y83t</t>
         </is>
       </c>
       <c r="X610" t="n">
@@ -68032,14 +68024,14 @@
       </c>
       <c r="Y610" t="inlineStr">
         <is>
-          <t>Greater Pitt Tree Service</t>
+          <t>Stroud Chiropractic PLLC</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>1216638001026912</t>
+          <t>1216669020714116</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -68054,7 +68046,7 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>Summer Rima</t>
+          <t>Madison McCaskey</t>
         </is>
       </c>
       <c r="E611" t="inlineStr"/>
@@ -68065,7 +68057,7 @@
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>2026-07-16 09:09:35</t>
+          <t>2026-07-17 13:14:42</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -68075,12 +68067,12 @@
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>2026-07-20 01:00:30</t>
+          <t>2026-07-20 21:08:53</t>
         </is>
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>2026-07-20 01:00:25</t>
+          <t>2026-07-20 21:08:51</t>
         </is>
       </c>
       <c r="K611" t="b">
@@ -68093,28 +68085,28 @@
       </c>
       <c r="M611" t="inlineStr">
         <is>
-          <t>BSDG2641</t>
+          <t>BRWJ6635</t>
         </is>
       </c>
       <c r="N611" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="O611" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="P611" t="n">
-        <v>11100</v>
+        <v>5200</v>
       </c>
       <c r="Q611" t="n">
-        <v>13100</v>
+        <v>6700</v>
       </c>
       <c r="R611" t="inlineStr">
         <is>
-          <t>Summer Rima</t>
+          <t>Madison McCaskey</t>
         </is>
       </c>
       <c r="S611" t="inlineStr">
@@ -68139,22 +68131,22 @@
       </c>
       <c r="W611" t="inlineStr">
         <is>
-          <t>ewhtpgcyc18ajv39</t>
+          <t>awtjpp33s3vhq5t2</t>
         </is>
       </c>
       <c r="X611" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="Y611" t="inlineStr">
         <is>
-          <t>EXT Enhancements Roofing &amp; Siding LLC</t>
+          <t>Boone Heating &amp; Air Conditioning Inc</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>1216638107677105</t>
+          <t>1216720207491318</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -68169,7 +68161,7 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>Glenys Rodriguez Gomez</t>
+          <t>David Ostendorf</t>
         </is>
       </c>
       <c r="E612" t="inlineStr"/>
@@ -68180,7 +68172,7 @@
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>2026-07-16 10:43:55</t>
+          <t>2026-07-20 08:18:44</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -68190,12 +68182,12 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>2026-07-20 00:36:29</t>
+          <t>2026-07-20 21:05:39</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>2026-07-20 00:36:26</t>
+          <t>2026-07-20 21:05:37</t>
         </is>
       </c>
       <c r="K612" t="b">
@@ -68208,59 +68200,511 @@
       </c>
       <c r="M612" t="inlineStr">
         <is>
+          <t>BRTH5137</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="P612" t="n">
+        <v>9200</v>
+      </c>
+      <c r="Q612" t="n">
+        <v>10700</v>
+      </c>
+      <c r="R612" t="inlineStr">
+        <is>
+          <t>David Ostendorf</t>
+        </is>
+      </c>
+      <c r="S612" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T612" t="inlineStr">
+        <is>
+          <t>Recommendation sent via email and closed by BA</t>
+        </is>
+      </c>
+      <c r="U612" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V612" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W612" t="inlineStr">
+        <is>
+          <t>nwurayxntxfif89x</t>
+        </is>
+      </c>
+      <c r="X612" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y612" t="inlineStr">
+        <is>
+          <t>Action Glass &amp; Mirror Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>1216730477297012</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Will King</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr"/>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Julia Cowden</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:30:59</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr"/>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:27:50</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:27:50</t>
+        </is>
+      </c>
+      <c r="K613" t="b">
+        <v>1</v>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>BSFP4473</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="P613" t="n">
+        <v>5400</v>
+      </c>
+      <c r="Q613" t="n">
+        <v>8000</v>
+      </c>
+      <c r="R613" t="inlineStr">
+        <is>
+          <t>Will King</t>
+        </is>
+      </c>
+      <c r="S613" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T613" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U613" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V613" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W613" t="inlineStr">
+        <is>
+          <t>6956994288</t>
+        </is>
+      </c>
+      <c r="X613" t="n">
+        <v>150</v>
+      </c>
+      <c r="Y613" t="inlineStr">
+        <is>
+          <t>the plumber's plumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>1216719974731854</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Jason Hockett</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr"/>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Julia Cowden</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:15:12</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr"/>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:26:38</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:26:38</t>
+        </is>
+      </c>
+      <c r="K614" t="b">
+        <v>1</v>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>BCQF1440</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="P614" t="n">
+        <v>3250</v>
+      </c>
+      <c r="Q614" t="n">
+        <v>3750</v>
+      </c>
+      <c r="R614" t="inlineStr">
+        <is>
+          <t>Jason Hockett</t>
+        </is>
+      </c>
+      <c r="S614" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T614" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U614" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V614" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W614" t="inlineStr">
+        <is>
+          <t>hy1p2soruemodicq</t>
+        </is>
+      </c>
+      <c r="X614" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y614" t="inlineStr">
+        <is>
+          <t>Greater Pitt Tree Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>1216638001026912</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Summer Rima</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr"/>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Dexter Tardy</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>2026-07-16 09:09:35</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>2026-07-20 01:00:30</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>2026-07-20 01:00:25</t>
+        </is>
+      </c>
+      <c r="K615" t="b">
+        <v>1</v>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>BSDG2641</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="P615" t="n">
+        <v>11100</v>
+      </c>
+      <c r="Q615" t="n">
+        <v>13100</v>
+      </c>
+      <c r="R615" t="inlineStr">
+        <is>
+          <t>Summer Rima</t>
+        </is>
+      </c>
+      <c r="S615" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T615" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U615" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V615" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W615" t="inlineStr">
+        <is>
+          <t>ewhtpgcyc18ajv39</t>
+        </is>
+      </c>
+      <c r="X615" t="n">
+        <v>150</v>
+      </c>
+      <c r="Y615" t="inlineStr">
+        <is>
+          <t>EXT Enhancements Roofing &amp; Siding LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>1216638107677105</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Glenys Rodriguez Gomez</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr"/>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Dexter Tardy</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:43:55</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>2026-07-20 00:36:29</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>2026-07-20 00:36:26</t>
+        </is>
+      </c>
+      <c r="K616" t="b">
+        <v>1</v>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
           <t xml:space="preserve"> BBJF0221</t>
         </is>
       </c>
-      <c r="N612" t="inlineStr">
+      <c r="N616" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="O612" t="inlineStr">
+      <c r="O616" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="P612" t="n">
+      <c r="P616" t="n">
         <v>250</v>
       </c>
-      <c r="Q612" t="n">
+      <c r="Q616" t="n">
         <v>400</v>
       </c>
-      <c r="R612" t="inlineStr">
+      <c r="R616" t="inlineStr">
         <is>
           <t>Glenys Rodriguez Gomez</t>
         </is>
       </c>
-      <c r="S612" t="inlineStr">
+      <c r="S616" t="inlineStr">
         <is>
           <t>Reoccurring Charge</t>
         </is>
       </c>
-      <c r="T612" t="inlineStr">
+      <c r="T616" t="inlineStr">
         <is>
           <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V612" t="inlineStr">
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V616" t="inlineStr">
         <is>
           <t>CER was closed already</t>
         </is>
       </c>
-      <c r="W612" t="inlineStr">
+      <c r="W616" t="inlineStr">
         <is>
           <t>CC_1C03CA819</t>
         </is>
       </c>
-      <c r="X612" t="n">
+      <c r="X616" t="n">
         <v>10</v>
       </c>
-      <c r="Y612" t="inlineStr">
+      <c r="Y616" t="inlineStr">
         <is>
           <t>Pizza And Stuff</t>
         </is>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y616"/>
+  <dimension ref="A1:Y622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66465,7 +66465,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>1216859696731429</t>
+          <t>1216837286315333</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -66480,29 +66480,29 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Yenifer Medina</t>
+          <t>Holly Fatla</t>
         </is>
       </c>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Dexter Tardy</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>2026-07-24 11:08:39</t>
+          <t>2026-07-23 14:57:41</t>
         </is>
       </c>
       <c r="H597" t="inlineStr"/>
       <c r="I597" t="inlineStr">
         <is>
-          <t>2026-07-24 14:44:38</t>
+          <t>2026-07-26 23:19:52</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>2026-07-24 14:44:38</t>
+          <t>2026-07-26 23:19:50</t>
         </is>
       </c>
       <c r="K597" t="b">
@@ -66510,33 +66510,33 @@
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>New Thryv Services: Strategic Content Creation</t>
         </is>
       </c>
       <c r="M597" t="inlineStr">
         <is>
-          <t>BLXJ4791</t>
+          <t>BSDJ9839</t>
         </is>
       </c>
       <c r="N597" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="P597" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Q597" t="n">
-        <v>3000</v>
+        <v>499</v>
       </c>
       <c r="R597" t="inlineStr">
         <is>
-          <t>Yenifer Medina</t>
+          <t>Holly Fatla</t>
         </is>
       </c>
       <c r="S597" t="inlineStr">
@@ -66546,7 +66546,7 @@
       </c>
       <c r="T597" t="inlineStr">
         <is>
-          <t>Recommendation sent via email and closed by BA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U597" t="inlineStr">
@@ -66561,22 +66561,22 @@
       </c>
       <c r="W597" t="inlineStr">
         <is>
-          <t>h9l6iu2ukgo9mq0a</t>
+          <t>wfamn9tf64jcsnkf</t>
         </is>
       </c>
       <c r="X597" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="Y597" t="inlineStr">
         <is>
-          <t>Marvs Quality Towing Service Inc</t>
+          <t>Sunshine Services</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>1216834529911207</t>
+          <t>1216836896356475</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -66591,29 +66591,29 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Holly Fatla</t>
         </is>
       </c>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Dexter Tardy</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>2026-07-23 13:11:33</t>
+          <t>2026-07-23 14:54:44</t>
         </is>
       </c>
       <c r="H598" t="inlineStr"/>
       <c r="I598" t="inlineStr">
         <is>
-          <t>2026-07-24 07:39:46</t>
+          <t>2026-07-26 23:15:26</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>2026-07-24 07:39:46</t>
+          <t>2026-07-26 23:15:22</t>
         </is>
       </c>
       <c r="K598" t="b">
@@ -66621,33 +66621,33 @@
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>SEO Increase</t>
         </is>
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>BSCT8166</t>
+          <t>BSDJ9839</t>
         </is>
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="P598" t="n">
-        <v>4700</v>
+        <v>900</v>
       </c>
       <c r="Q598" t="n">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="R598" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Holly Fatla</t>
         </is>
       </c>
       <c r="S598" t="inlineStr">
@@ -66657,7 +66657,7 @@
       </c>
       <c r="T598" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U598" t="inlineStr">
@@ -66672,22 +66672,22 @@
       </c>
       <c r="W598" t="inlineStr">
         <is>
-          <t>LOC151D97BB3</t>
+          <t>wfamn9tf64jcsnkf</t>
         </is>
       </c>
       <c r="X598" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="Y598" t="inlineStr">
         <is>
-          <t>Kay's Affordable HVAC&amp;R</t>
+          <t>Sunshine Services</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>1216840244857332</t>
+          <t>1216837627861767</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -66702,29 +66702,29 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Alicia Battiata</t>
+          <t>Holly Fatla</t>
         </is>
       </c>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Dexter Tardy</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>2026-07-23 17:53:24</t>
+          <t>2026-07-23 15:20:29</t>
         </is>
       </c>
       <c r="H599" t="inlineStr"/>
       <c r="I599" t="inlineStr">
         <is>
-          <t>2026-07-24 07:38:43</t>
+          <t>2026-07-26 23:12:19</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>2026-07-24 07:38:39</t>
+          <t>2026-07-26 23:12:16</t>
         </is>
       </c>
       <c r="K599" t="b">
@@ -66732,33 +66732,33 @@
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>New Thryv Social Ads</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>BSFB4678</t>
+          <t>BCSJ1962</t>
         </is>
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="P599" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Q599" t="n">
-        <v>500</v>
+        <v>11000</v>
       </c>
       <c r="R599" t="inlineStr">
         <is>
-          <t>Alicia Battiata</t>
+          <t>Holly Fatla</t>
         </is>
       </c>
       <c r="S599" t="inlineStr">
@@ -66783,22 +66783,22 @@
       </c>
       <c r="W599" t="inlineStr">
         <is>
-          <t>cxoh9nldc0b9vi4n</t>
+          <t>6zng9pz2wjlcuimz</t>
         </is>
       </c>
       <c r="X599" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="Y599" t="inlineStr">
         <is>
-          <t>Vital Drip Lounge</t>
+          <t>DeShazo and Son Roofing</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>1216840107980282</t>
+          <t>1216838036646535</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -66813,29 +66813,29 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ruchi Sharma </t>
+          <t>Holly Fatla</t>
         </is>
       </c>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Julian Komimbin</t>
+          <t>Dexter Tardy</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>2026-07-23 17:37:58</t>
+          <t>2026-07-23 15:32:57</t>
         </is>
       </c>
       <c r="H600" t="inlineStr"/>
       <c r="I600" t="inlineStr">
         <is>
-          <t>2026-07-24 04:08:13</t>
+          <t>2026-07-26 23:12:28</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>2026-07-24 04:08:04</t>
+          <t>2026-07-26 23:12:28</t>
         </is>
       </c>
       <c r="K600" t="b">
@@ -66843,33 +66843,33 @@
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>New SEO</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>BSCZ5289</t>
+          <t>BRRZ3102</t>
         </is>
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P600" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="Q600" t="n">
-        <v>875</v>
+        <v>2350</v>
       </c>
       <c r="R600" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ruchi Sharma </t>
+          <t>Holly Fatla</t>
         </is>
       </c>
       <c r="S600" t="inlineStr">
@@ -66879,7 +66879,7 @@
       </c>
       <c r="T600" t="inlineStr">
         <is>
-          <t>Recommendation sent via email and closed by BA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U600" t="inlineStr">
@@ -66889,27 +66889,27 @@
       </c>
       <c r="V600" t="inlineStr">
         <is>
-          <t>CER Still In Progress</t>
+          <t>CER was closed already</t>
         </is>
       </c>
       <c r="W600" t="inlineStr">
         <is>
-          <t>LOC119AABF3B</t>
+          <t>LOC179B88B83</t>
         </is>
       </c>
       <c r="X600" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="Y600" t="inlineStr">
         <is>
-          <t>AARON JOHN BRADLEY</t>
+          <t>Mr. Plumber</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>1216817593298502</t>
+          <t>1216837909024872</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -66924,29 +66924,29 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Chyna Elias</t>
+          <t>Holly Fatla</t>
         </is>
       </c>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Shannon Comas</t>
+          <t>Dexter Tardy</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>2026-07-22 14:04:48</t>
+          <t>2026-07-23 15:34:03</t>
         </is>
       </c>
       <c r="H601" t="inlineStr"/>
       <c r="I601" t="inlineStr">
         <is>
-          <t>2026-07-23 09:37:25</t>
+          <t>2026-07-26 23:07:08</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>2026-07-23 09:37:23</t>
+          <t>2026-07-26 23:07:06</t>
         </is>
       </c>
       <c r="K601" t="b">
@@ -66954,33 +66954,33 @@
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>New MC</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M601" t="inlineStr">
         <is>
-          <t>BSCJ7580</t>
+          <t>BRRZ3102</t>
         </is>
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P601" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="Q601" t="n">
-        <v>255</v>
+        <v>1750</v>
       </c>
       <c r="R601" t="inlineStr">
         <is>
-          <t>Chyna Elias</t>
+          <t>Holly Fatla</t>
         </is>
       </c>
       <c r="S601" t="inlineStr">
@@ -67005,22 +67005,22 @@
       </c>
       <c r="W601" t="inlineStr">
         <is>
-          <t>Wv16qg0616cl6jwp</t>
+          <t>LOC142711C3</t>
         </is>
       </c>
       <c r="X601" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y601" t="inlineStr">
         <is>
-          <t>Republic of Texas Concrete Coatings</t>
+          <t>Mr. Plumber</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>1216662060845690</t>
+          <t>1216834847419131</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -67035,7 +67035,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Lauren Crutchfield</t>
+          <t>Chyna Elias</t>
         </is>
       </c>
       <c r="E602" t="inlineStr"/>
@@ -67046,22 +67046,18 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>2026-07-17 09:39:28</t>
-        </is>
-      </c>
-      <c r="H602" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
+          <t>2026-07-23 13:36:51</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr"/>
       <c r="I602" t="inlineStr">
         <is>
-          <t>2026-07-23 09:36:08</t>
+          <t>2026-07-26 21:34:07</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>2026-07-23 09:36:06</t>
+          <t>2026-07-26 21:34:05</t>
         </is>
       </c>
       <c r="K602" t="b">
@@ -67069,33 +67065,33 @@
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>New Thryv Social Ads</t>
         </is>
       </c>
       <c r="M602" t="inlineStr">
         <is>
-          <t>BCKG2302</t>
+          <t>BRWP2489</t>
         </is>
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="P602" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="Q602" t="n">
-        <v>2300</v>
+        <v>750</v>
       </c>
       <c r="R602" t="inlineStr">
         <is>
-          <t>Lauren Crutchfield</t>
+          <t>Chyna Elias</t>
         </is>
       </c>
       <c r="S602" t="inlineStr">
@@ -67115,12 +67111,12 @@
       </c>
       <c r="V602" t="inlineStr">
         <is>
-          <t>CER Still In Progress</t>
+          <t>CER was closed already</t>
         </is>
       </c>
       <c r="W602" t="inlineStr">
         <is>
-          <t>cifelhaaqpmnt6s2</t>
+          <t>b58dwlbshnivcjxg</t>
         </is>
       </c>
       <c r="X602" t="n">
@@ -67128,14 +67124,14 @@
       </c>
       <c r="Y602" t="inlineStr">
         <is>
-          <t>The Law Offices of Paul S Missan</t>
+          <t>Cohen Law Offices LLC</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>1216728742070253</t>
+          <t>1216859696731429</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -67150,33 +67146,29 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Taylor Sloan</t>
+          <t>Yenifer Medina</t>
         </is>
       </c>
       <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Shannon Comas</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>2026-07-20 11:41:38</t>
-        </is>
-      </c>
-      <c r="H603" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
+          <t>2026-07-24 11:08:39</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr"/>
       <c r="I603" t="inlineStr">
         <is>
-          <t>2026-07-22 21:03:14</t>
+          <t>2026-07-24 14:44:38</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>2026-07-22 21:03:11</t>
+          <t>2026-07-24 14:44:38</t>
         </is>
       </c>
       <c r="K603" t="b">
@@ -67189,28 +67181,28 @@
       </c>
       <c r="M603" t="inlineStr">
         <is>
-          <t>BRXF8435</t>
+          <t>BLXJ4791</t>
         </is>
       </c>
       <c r="N603" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="P603" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="Q603" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="R603" t="inlineStr">
         <is>
-          <t>Taylor Sloan</t>
+          <t>Yenifer Medina</t>
         </is>
       </c>
       <c r="S603" t="inlineStr">
@@ -67235,7 +67227,7 @@
       </c>
       <c r="W603" t="inlineStr">
         <is>
-          <t>bn06kt84woog63bo</t>
+          <t>h9l6iu2ukgo9mq0a</t>
         </is>
       </c>
       <c r="X603" t="n">
@@ -67243,14 +67235,14 @@
       </c>
       <c r="Y603" t="inlineStr">
         <is>
-          <t>Low Price Auto Glass</t>
+          <t>Marvs Quality Towing Service Inc</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>1216769215852730</t>
+          <t>1216834529911207</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -67265,33 +67257,29 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Scott Jennings</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="E604" t="inlineStr"/>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Shannon Comas</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>2026-07-21 14:54:55</t>
-        </is>
-      </c>
-      <c r="H604" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
+          <t>2026-07-23 13:11:33</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr"/>
       <c r="I604" t="inlineStr">
         <is>
-          <t>2026-07-22 16:48:13</t>
+          <t>2026-07-24 07:39:46</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>2026-07-22 16:48:11</t>
+          <t>2026-07-24 07:39:46</t>
         </is>
       </c>
       <c r="K604" t="b">
@@ -67304,28 +67292,28 @@
       </c>
       <c r="M604" t="inlineStr">
         <is>
-          <t>BRWQ3469</t>
+          <t>BSCT8166</t>
         </is>
       </c>
       <c r="N604" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="P604" t="n">
-        <v>6250</v>
+        <v>4700</v>
       </c>
       <c r="Q604" t="n">
-        <v>9250</v>
+        <v>7000</v>
       </c>
       <c r="R604" t="inlineStr">
         <is>
-          <t>Scott Jennings</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="S604" t="inlineStr">
@@ -67335,7 +67323,7 @@
       </c>
       <c r="T604" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U604" t="inlineStr">
@@ -67345,12 +67333,12 @@
       </c>
       <c r="V604" t="inlineStr">
         <is>
-          <t>CER Still In Progress</t>
+          <t>CER was closed already</t>
         </is>
       </c>
       <c r="W604" t="inlineStr">
         <is>
-          <t>Q3ND03P</t>
+          <t>LOC151D97BB3</t>
         </is>
       </c>
       <c r="X604" t="n">
@@ -67358,14 +67346,14 @@
       </c>
       <c r="Y604" t="inlineStr">
         <is>
-          <t>Vaccine Injury Lawyers</t>
+          <t>Kay's Affordable HVAC&amp;R</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>1216772425817699</t>
+          <t>1216840244857332</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -67380,33 +67368,29 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Dominic Ondabu</t>
+          <t>Alicia Battiata</t>
         </is>
       </c>
       <c r="E605" t="inlineStr"/>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Shannon Comas</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>2026-07-21 17:54:21</t>
-        </is>
-      </c>
-      <c r="H605" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
+          <t>2026-07-23 17:53:24</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr"/>
       <c r="I605" t="inlineStr">
         <is>
-          <t>2026-07-22 16:45:24</t>
+          <t>2026-07-24 07:38:43</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>2026-07-22 16:45:22</t>
+          <t>2026-07-24 07:38:39</t>
         </is>
       </c>
       <c r="K605" t="b">
@@ -67414,33 +67398,33 @@
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>SEO Increase</t>
+          <t>New Thryv Social Ads</t>
         </is>
       </c>
       <c r="M605" t="inlineStr">
         <is>
-          <t>BFLH4868</t>
+          <t>BSFB4678</t>
         </is>
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="P605" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="Q605" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="R605" t="inlineStr">
         <is>
-          <t>Dominic Ondabu</t>
+          <t>Alicia Battiata</t>
         </is>
       </c>
       <c r="S605" t="inlineStr">
@@ -67465,7 +67449,7 @@
       </c>
       <c r="W605" t="inlineStr">
         <is>
-          <t>jhu5xzfqdmkx7zfr</t>
+          <t>cxoh9nldc0b9vi4n</t>
         </is>
       </c>
       <c r="X605" t="n">
@@ -67473,14 +67457,14 @@
       </c>
       <c r="Y605" t="inlineStr">
         <is>
-          <t>Law Office of Carlos Molinar</t>
+          <t>Vital Drip Lounge</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>1216789986150810</t>
+          <t>1216840107980282</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -67495,29 +67479,29 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t xml:space="preserve">Ruchi Sharma </t>
         </is>
       </c>
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Julian Komimbin</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>2026-07-22 08:59:21</t>
+          <t>2026-07-23 17:37:58</t>
         </is>
       </c>
       <c r="H606" t="inlineStr"/>
       <c r="I606" t="inlineStr">
         <is>
-          <t>2026-07-22 13:06:11</t>
+          <t>2026-07-24 04:08:13</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>2026-07-22 13:06:11</t>
+          <t>2026-07-24 04:08:04</t>
         </is>
       </c>
       <c r="K606" t="b">
@@ -67525,33 +67509,33 @@
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>New SEO</t>
         </is>
       </c>
       <c r="M606" t="inlineStr">
         <is>
-          <t>BRXF0778</t>
+          <t>BSCZ5289</t>
         </is>
       </c>
       <c r="N606" t="inlineStr">
         <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="O606" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
       <c r="P606" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="Q606" t="n">
-        <v>8000</v>
+        <v>875</v>
       </c>
       <c r="R606" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t xml:space="preserve">Ruchi Sharma </t>
         </is>
       </c>
       <c r="S606" t="inlineStr">
@@ -67561,7 +67545,7 @@
       </c>
       <c r="T606" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
       <c r="U606" t="inlineStr">
@@ -67571,27 +67555,27 @@
       </c>
       <c r="V606" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W606" t="inlineStr">
         <is>
-          <t>80i4envpy4li3wu7</t>
+          <t>LOC119AABF3B</t>
         </is>
       </c>
       <c r="X606" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="Y606" t="inlineStr">
         <is>
-          <t>H&amp;H Plumbing Contractors</t>
+          <t>AARON JOHN BRADLEY</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>1216761973595601</t>
+          <t>1216817593298502</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -67606,33 +67590,29 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Staci Maples</t>
+          <t>Chyna Elias</t>
         </is>
       </c>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Carla Miner-Luginbyhl</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>2026-07-21 10:54:06</t>
-        </is>
-      </c>
-      <c r="H607" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
+          <t>2026-07-22 14:04:48</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr"/>
       <c r="I607" t="inlineStr">
         <is>
-          <t>2026-07-22 12:04:27</t>
+          <t>2026-07-23 09:37:25</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>2026-07-22 12:04:24</t>
+          <t>2026-07-23 09:37:23</t>
         </is>
       </c>
       <c r="K607" t="b">
@@ -67640,32 +67620,40 @@
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>New MC</t>
         </is>
       </c>
       <c r="M607" t="inlineStr">
         <is>
-          <t>BSFZ1940</t>
+          <t>BSCJ7580</t>
         </is>
       </c>
       <c r="N607" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="O607" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="P607" t="inlineStr"/>
-      <c r="Q607" t="inlineStr"/>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="P607" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q607" t="n">
+        <v>255</v>
+      </c>
       <c r="R607" t="inlineStr">
         <is>
-          <t>Staci Maples</t>
-        </is>
-      </c>
-      <c r="S607" t="inlineStr"/>
+          <t>Chyna Elias</t>
+        </is>
+      </c>
+      <c r="S607" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
       <c r="T607" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -67683,20 +67671,22 @@
       </c>
       <c r="W607" t="inlineStr">
         <is>
-          <t>LOCE5E4814B</t>
-        </is>
-      </c>
-      <c r="X607" t="inlineStr"/>
+          <t>Wv16qg0616cl6jwp</t>
+        </is>
+      </c>
+      <c r="X607" t="n">
+        <v>0</v>
+      </c>
       <c r="Y607" t="inlineStr">
         <is>
-          <t>Nature Tree Service</t>
+          <t>Republic of Texas Concrete Coatings</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>1216251694736989</t>
+          <t>1216662060845690</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -67711,33 +67701,33 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Antonio Perez</t>
+          <t>Lauren Crutchfield</t>
         </is>
       </c>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Carla Miner-Luginbyhl</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>2026-07-02 15:53:18</t>
+          <t>2026-07-17 09:39:28</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>2026-07-22 11:56:55</t>
+          <t>2026-07-23 09:36:08</t>
         </is>
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>2026-07-22 11:56:04</t>
+          <t>2026-07-23 09:36:06</t>
         </is>
       </c>
       <c r="K608" t="b">
@@ -67745,33 +67735,33 @@
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>New SEO</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M608" t="inlineStr">
         <is>
-          <t>BRXH9480</t>
+          <t>BCKG2302</t>
         </is>
       </c>
       <c r="N608" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O608" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="P608" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="Q608" t="n">
-        <v>2700</v>
+        <v>2300</v>
       </c>
       <c r="R608" t="inlineStr">
         <is>
-          <t>Antonio Perez</t>
+          <t>Lauren Crutchfield</t>
         </is>
       </c>
       <c r="S608" t="inlineStr">
@@ -67796,20 +67786,22 @@
       </c>
       <c r="W608" t="inlineStr">
         <is>
-          <t>LOCDAD72547</t>
-        </is>
-      </c>
-      <c r="X608" t="inlineStr"/>
+          <t>cifelhaaqpmnt6s2</t>
+        </is>
+      </c>
+      <c r="X608" t="n">
+        <v>25</v>
+      </c>
       <c r="Y608" t="inlineStr">
         <is>
-          <t>Ernies Plumbing &amp; Sewer Service</t>
+          <t>The Law Offices of Paul S Missan</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>1216739682296057</t>
+          <t>1216728742070253</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -67824,29 +67816,33 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Mansi Aggarwal</t>
+          <t>Taylor Sloan</t>
         </is>
       </c>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Julian Komimbin</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>2026-07-20 21:13:35</t>
-        </is>
-      </c>
-      <c r="H609" t="inlineStr"/>
+          <t>2026-07-20 11:41:38</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>2026-07-21 17:25:43</t>
+          <t>2026-07-22 21:03:14</t>
         </is>
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>2026-07-21 17:25:18</t>
+          <t>2026-07-22 21:03:11</t>
         </is>
       </c>
       <c r="K609" t="b">
@@ -67854,33 +67850,33 @@
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>SaaS Add-On</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M609" t="inlineStr">
         <is>
-          <t>BSGC2255</t>
+          <t>BRXF8435</t>
         </is>
       </c>
       <c r="N609" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="O609" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="P609" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="Q609" t="n">
-        <v>150</v>
+        <v>3500</v>
       </c>
       <c r="R609" t="inlineStr">
         <is>
-          <t>Mansi Aggarwal</t>
+          <t>Taylor Sloan</t>
         </is>
       </c>
       <c r="S609" t="inlineStr">
@@ -67890,7 +67886,7 @@
       </c>
       <c r="T609" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
       <c r="U609" t="inlineStr">
@@ -67900,27 +67896,27 @@
       </c>
       <c r="V609" t="inlineStr">
         <is>
-          <t>CER Still In Progress</t>
+          <t>CER was closed already</t>
         </is>
       </c>
       <c r="W609" t="inlineStr">
         <is>
-          <t>LOC162FA8667</t>
+          <t>bn06kt84woog63bo</t>
         </is>
       </c>
       <c r="X609" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="Y609" t="inlineStr">
         <is>
-          <t>TTW tilers trade warehouse</t>
+          <t>Low Price Auto Glass</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>1216672722760559</t>
+          <t>1216769215852730</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -67935,29 +67931,33 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Scott Jennings</t>
         </is>
       </c>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>2026-07-17 16:06:47</t>
-        </is>
-      </c>
-      <c r="H610" t="inlineStr"/>
+          <t>2026-07-21 14:54:55</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>2026-07-21 09:18:14</t>
+          <t>2026-07-22 16:48:13</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>2026-07-21 09:18:14</t>
+          <t>2026-07-22 16:48:11</t>
         </is>
       </c>
       <c r="K610" t="b">
@@ -67965,33 +67965,33 @@
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t>New Thryv Social Ads</t>
+          <t>TL Increase</t>
         </is>
       </c>
       <c r="M610" t="inlineStr">
         <is>
-          <t>BSCB8068</t>
+          <t>BRWQ3469</t>
         </is>
       </c>
       <c r="N610" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="O610" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P610" t="n">
-        <v>0</v>
+        <v>6250</v>
       </c>
       <c r="Q610" t="n">
-        <v>500</v>
+        <v>9250</v>
       </c>
       <c r="R610" t="inlineStr">
         <is>
-          <t>La'Donna Williams</t>
+          <t>Scott Jennings</t>
         </is>
       </c>
       <c r="S610" t="inlineStr">
@@ -68001,7 +68001,7 @@
       </c>
       <c r="T610" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U610" t="inlineStr">
@@ -68011,27 +68011,27 @@
       </c>
       <c r="V610" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W610" t="inlineStr">
         <is>
-          <t>de846yo0m1x1y83t</t>
+          <t>Q3ND03P</t>
         </is>
       </c>
       <c r="X610" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="Y610" t="inlineStr">
         <is>
-          <t>Stroud Chiropractic PLLC</t>
+          <t>Vaccine Injury Lawyers</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>1216669020714116</t>
+          <t>1216772425817699</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -68046,33 +68046,33 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>Madison McCaskey</t>
+          <t>Dominic Ondabu</t>
         </is>
       </c>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Shannon Comas</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>2026-07-17 13:14:42</t>
+          <t>2026-07-21 17:54:21</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>2026-07-20 21:08:53</t>
+          <t>2026-07-22 16:45:24</t>
         </is>
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>2026-07-20 21:08:51</t>
+          <t>2026-07-22 16:45:22</t>
         </is>
       </c>
       <c r="K611" t="b">
@@ -68080,33 +68080,33 @@
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>SEO Increase</t>
         </is>
       </c>
       <c r="M611" t="inlineStr">
         <is>
-          <t>BRWJ6635</t>
+          <t>BFLH4868</t>
         </is>
       </c>
       <c r="N611" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="O611" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="P611" t="n">
-        <v>5200</v>
+        <v>1100</v>
       </c>
       <c r="Q611" t="n">
-        <v>6700</v>
+        <v>1500</v>
       </c>
       <c r="R611" t="inlineStr">
         <is>
-          <t>Madison McCaskey</t>
+          <t>Dominic Ondabu</t>
         </is>
       </c>
       <c r="S611" t="inlineStr">
@@ -68116,7 +68116,7 @@
       </c>
       <c r="T611" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U611" t="inlineStr">
@@ -68131,22 +68131,22 @@
       </c>
       <c r="W611" t="inlineStr">
         <is>
-          <t>awtjpp33s3vhq5t2</t>
+          <t>jhu5xzfqdmkx7zfr</t>
         </is>
       </c>
       <c r="X611" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="Y611" t="inlineStr">
         <is>
-          <t>Boone Heating &amp; Air Conditioning Inc</t>
+          <t>Law Office of Carlos Molinar</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>1216720207491318</t>
+          <t>1216789986150810</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -68161,33 +68161,29 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>David Ostendorf</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="E612" t="inlineStr"/>
       <c r="F612" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>2026-07-20 08:18:44</t>
-        </is>
-      </c>
-      <c r="H612" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+          <t>2026-07-22 08:59:21</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr"/>
       <c r="I612" t="inlineStr">
         <is>
-          <t>2026-07-20 21:05:39</t>
+          <t>2026-07-22 13:06:11</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>2026-07-20 21:05:37</t>
+          <t>2026-07-22 13:06:11</t>
         </is>
       </c>
       <c r="K612" t="b">
@@ -68200,28 +68196,28 @@
       </c>
       <c r="M612" t="inlineStr">
         <is>
-          <t>BRTH5137</t>
+          <t>BRXF0778</t>
         </is>
       </c>
       <c r="N612" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="O612" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P612" t="n">
-        <v>9200</v>
+        <v>7000</v>
       </c>
       <c r="Q612" t="n">
-        <v>10700</v>
+        <v>8000</v>
       </c>
       <c r="R612" t="inlineStr">
         <is>
-          <t>David Ostendorf</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="S612" t="inlineStr">
@@ -68231,7 +68227,7 @@
       </c>
       <c r="T612" t="inlineStr">
         <is>
-          <t>Recommendation sent via email and closed by BA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U612" t="inlineStr">
@@ -68246,7 +68242,7 @@
       </c>
       <c r="W612" t="inlineStr">
         <is>
-          <t>nwurayxntxfif89x</t>
+          <t>80i4envpy4li3wu7</t>
         </is>
       </c>
       <c r="X612" t="n">
@@ -68254,14 +68250,14 @@
       </c>
       <c r="Y612" t="inlineStr">
         <is>
-          <t>Action Glass &amp; Mirror Inc</t>
+          <t>H&amp;H Plumbing Contractors</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>1216730477297012</t>
+          <t>1216761973595601</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -68276,29 +68272,33 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>Will King</t>
+          <t>Staci Maples</t>
         </is>
       </c>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Carla Miner-Luginbyhl</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>2026-07-20 12:30:59</t>
-        </is>
-      </c>
-      <c r="H613" t="inlineStr"/>
+          <t>2026-07-21 10:54:06</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>2026-07-20 13:27:50</t>
+          <t>2026-07-22 12:04:27</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>2026-07-20 13:27:50</t>
+          <t>2026-07-22 12:04:24</t>
         </is>
       </c>
       <c r="K613" t="b">
@@ -68311,35 +68311,27 @@
       </c>
       <c r="M613" t="inlineStr">
         <is>
-          <t>BSFP4473</t>
+          <t>BSFZ1940</t>
         </is>
       </c>
       <c r="N613" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O613" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="P613" t="n">
-        <v>5400</v>
-      </c>
-      <c r="Q613" t="n">
-        <v>8000</v>
-      </c>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P613" t="inlineStr"/>
+      <c r="Q613" t="inlineStr"/>
       <c r="R613" t="inlineStr">
         <is>
-          <t>Will King</t>
-        </is>
-      </c>
-      <c r="S613" t="inlineStr">
-        <is>
-          <t>Reoccurring Charge</t>
-        </is>
-      </c>
+          <t>Staci Maples</t>
+        </is>
+      </c>
+      <c r="S613" t="inlineStr"/>
       <c r="T613" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -68357,22 +68349,20 @@
       </c>
       <c r="W613" t="inlineStr">
         <is>
-          <t>6956994288</t>
-        </is>
-      </c>
-      <c r="X613" t="n">
-        <v>150</v>
-      </c>
+          <t>LOCE5E4814B</t>
+        </is>
+      </c>
+      <c r="X613" t="inlineStr"/>
       <c r="Y613" t="inlineStr">
         <is>
-          <t>the plumber's plumber</t>
+          <t>Nature Tree Service</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>1216719974731854</t>
+          <t>1216251694736989</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -68387,29 +68377,33 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Jason Hockett</t>
+          <t>Antonio Perez</t>
         </is>
       </c>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Julia Cowden</t>
+          <t>Carla Miner-Luginbyhl</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>2026-07-20 08:15:12</t>
-        </is>
-      </c>
-      <c r="H614" t="inlineStr"/>
+          <t>2026-07-02 15:53:18</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
       <c r="I614" t="inlineStr">
         <is>
-          <t>2026-07-20 13:26:38</t>
+          <t>2026-07-22 11:56:55</t>
         </is>
       </c>
       <c r="J614" t="inlineStr">
         <is>
-          <t>2026-07-20 13:26:38</t>
+          <t>2026-07-22 11:56:04</t>
         </is>
       </c>
       <c r="K614" t="b">
@@ -68417,33 +68411,33 @@
       </c>
       <c r="L614" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>New SEO</t>
         </is>
       </c>
       <c r="M614" t="inlineStr">
         <is>
-          <t>BCQF1440</t>
+          <t>BRXH9480</t>
         </is>
       </c>
       <c r="N614" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="O614" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P614" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="Q614" t="n">
-        <v>3750</v>
+        <v>2700</v>
       </c>
       <c r="R614" t="inlineStr">
         <is>
-          <t>Jason Hockett</t>
+          <t>Antonio Perez</t>
         </is>
       </c>
       <c r="S614" t="inlineStr">
@@ -68463,27 +68457,25 @@
       </c>
       <c r="V614" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W614" t="inlineStr">
         <is>
-          <t>hy1p2soruemodicq</t>
-        </is>
-      </c>
-      <c r="X614" t="n">
-        <v>25</v>
-      </c>
+          <t>LOCDAD72547</t>
+        </is>
+      </c>
+      <c r="X614" t="inlineStr"/>
       <c r="Y614" t="inlineStr">
         <is>
-          <t>Greater Pitt Tree Service</t>
+          <t>Ernies Plumbing &amp; Sewer Service</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>1216638001026912</t>
+          <t>1216739682296057</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -68498,33 +68490,29 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Summer Rima</t>
+          <t>Mansi Aggarwal</t>
         </is>
       </c>
       <c r="E615" t="inlineStr"/>
       <c r="F615" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Julian Komimbin</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>2026-07-16 09:09:35</t>
-        </is>
-      </c>
-      <c r="H615" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+          <t>2026-07-20 21:13:35</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr"/>
       <c r="I615" t="inlineStr">
         <is>
-          <t>2026-07-20 01:00:30</t>
+          <t>2026-07-21 17:25:43</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>2026-07-20 01:00:25</t>
+          <t>2026-07-21 17:25:18</t>
         </is>
       </c>
       <c r="K615" t="b">
@@ -68532,33 +68520,33 @@
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t>TL Increase</t>
+          <t>SaaS Add-On</t>
         </is>
       </c>
       <c r="M615" t="inlineStr">
         <is>
-          <t>BSDG2641</t>
+          <t>BSGC2255</t>
         </is>
       </c>
       <c r="N615" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O615" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="P615" t="n">
-        <v>11100</v>
+        <v>0</v>
       </c>
       <c r="Q615" t="n">
-        <v>13100</v>
+        <v>150</v>
       </c>
       <c r="R615" t="inlineStr">
         <is>
-          <t>Summer Rima</t>
+          <t>Mansi Aggarwal</t>
         </is>
       </c>
       <c r="S615" t="inlineStr">
@@ -68568,7 +68556,7 @@
       </c>
       <c r="T615" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U615" t="inlineStr">
@@ -68578,27 +68566,27 @@
       </c>
       <c r="V615" t="inlineStr">
         <is>
-          <t>CER was closed already</t>
+          <t>CER Still In Progress</t>
         </is>
       </c>
       <c r="W615" t="inlineStr">
         <is>
-          <t>ewhtpgcyc18ajv39</t>
+          <t>LOC162FA8667</t>
         </is>
       </c>
       <c r="X615" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="Y615" t="inlineStr">
         <is>
-          <t>EXT Enhancements Roofing &amp; Siding LLC</t>
+          <t>TTW tilers trade warehouse</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>1216638107677105</t>
+          <t>1216672722760559</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -68613,33 +68601,29 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Glenys Rodriguez Gomez</t>
+          <t>La'Donna Williams</t>
         </is>
       </c>
       <c r="E616" t="inlineStr"/>
       <c r="F616" t="inlineStr">
         <is>
-          <t>Dexter Tardy</t>
+          <t>Julia Cowden</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>2026-07-16 10:43:55</t>
-        </is>
-      </c>
-      <c r="H616" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+          <t>2026-07-17 16:06:47</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr"/>
       <c r="I616" t="inlineStr">
         <is>
-          <t>2026-07-20 00:36:29</t>
+          <t>2026-07-21 09:18:14</t>
         </is>
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>2026-07-20 00:36:26</t>
+          <t>2026-07-21 09:18:14</t>
         </is>
       </c>
       <c r="K616" t="b">
@@ -68647,64 +68631,746 @@
       </c>
       <c r="L616" t="inlineStr">
         <is>
+          <t>New Thryv Social Ads</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>BSCB8068</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="P616" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q616" t="n">
+        <v>500</v>
+      </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>La'Donna Williams</t>
+        </is>
+      </c>
+      <c r="S616" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T616" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V616" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W616" t="inlineStr">
+        <is>
+          <t>de846yo0m1x1y83t</t>
+        </is>
+      </c>
+      <c r="X616" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y616" t="inlineStr">
+        <is>
+          <t>Stroud Chiropractic PLLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>1216669020714116</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Madison McCaskey</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr"/>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Dexter Tardy</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>2026-07-17 13:14:42</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:08:53</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:08:51</t>
+        </is>
+      </c>
+      <c r="K617" t="b">
+        <v>1</v>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
           <t>TL Increase</t>
         </is>
       </c>
-      <c r="M616" t="inlineStr">
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>BRWJ6635</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="P617" t="n">
+        <v>5200</v>
+      </c>
+      <c r="Q617" t="n">
+        <v>6700</v>
+      </c>
+      <c r="R617" t="inlineStr">
+        <is>
+          <t>Madison McCaskey</t>
+        </is>
+      </c>
+      <c r="S617" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T617" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U617" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V617" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W617" t="inlineStr">
+        <is>
+          <t>awtjpp33s3vhq5t2</t>
+        </is>
+      </c>
+      <c r="X617" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y617" t="inlineStr">
+        <is>
+          <t>Boone Heating &amp; Air Conditioning Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>1216720207491318</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>David Ostendorf</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr"/>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Dexter Tardy</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:18:44</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:05:39</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:05:37</t>
+        </is>
+      </c>
+      <c r="K618" t="b">
+        <v>1</v>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>BRTH5137</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="P618" t="n">
+        <v>9200</v>
+      </c>
+      <c r="Q618" t="n">
+        <v>10700</v>
+      </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>David Ostendorf</t>
+        </is>
+      </c>
+      <c r="S618" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T618" t="inlineStr">
+        <is>
+          <t>Recommendation sent via email and closed by BA</t>
+        </is>
+      </c>
+      <c r="U618" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V618" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W618" t="inlineStr">
+        <is>
+          <t>nwurayxntxfif89x</t>
+        </is>
+      </c>
+      <c r="X618" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y618" t="inlineStr">
+        <is>
+          <t>Action Glass &amp; Mirror Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>1216730477297012</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Will King</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr"/>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Julia Cowden</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:30:59</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr"/>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:27:50</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:27:50</t>
+        </is>
+      </c>
+      <c r="K619" t="b">
+        <v>1</v>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>BSFP4473</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="P619" t="n">
+        <v>5400</v>
+      </c>
+      <c r="Q619" t="n">
+        <v>8000</v>
+      </c>
+      <c r="R619" t="inlineStr">
+        <is>
+          <t>Will King</t>
+        </is>
+      </c>
+      <c r="S619" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T619" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U619" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V619" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W619" t="inlineStr">
+        <is>
+          <t>6956994288</t>
+        </is>
+      </c>
+      <c r="X619" t="n">
+        <v>150</v>
+      </c>
+      <c r="Y619" t="inlineStr">
+        <is>
+          <t>the plumber's plumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>1216719974731854</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Jason Hockett</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr"/>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Julia Cowden</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:15:12</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr"/>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:26:38</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:26:38</t>
+        </is>
+      </c>
+      <c r="K620" t="b">
+        <v>1</v>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>BCQF1440</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="P620" t="n">
+        <v>3250</v>
+      </c>
+      <c r="Q620" t="n">
+        <v>3750</v>
+      </c>
+      <c r="R620" t="inlineStr">
+        <is>
+          <t>Jason Hockett</t>
+        </is>
+      </c>
+      <c r="S620" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T620" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U620" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V620" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W620" t="inlineStr">
+        <is>
+          <t>hy1p2soruemodicq</t>
+        </is>
+      </c>
+      <c r="X620" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y620" t="inlineStr">
+        <is>
+          <t>Greater Pitt Tree Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>1216638001026912</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Summer Rima</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr"/>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Dexter Tardy</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>2026-07-16 09:09:35</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>2026-07-20 01:00:30</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>2026-07-20 01:00:25</t>
+        </is>
+      </c>
+      <c r="K621" t="b">
+        <v>1</v>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>BSDG2641</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="P621" t="n">
+        <v>11100</v>
+      </c>
+      <c r="Q621" t="n">
+        <v>13100</v>
+      </c>
+      <c r="R621" t="inlineStr">
+        <is>
+          <t>Summer Rima</t>
+        </is>
+      </c>
+      <c r="S621" t="inlineStr">
+        <is>
+          <t>Reoccurring Charge</t>
+        </is>
+      </c>
+      <c r="T621" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U621" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V621" t="inlineStr">
+        <is>
+          <t>CER was closed already</t>
+        </is>
+      </c>
+      <c r="W621" t="inlineStr">
+        <is>
+          <t>ewhtpgcyc18ajv39</t>
+        </is>
+      </c>
+      <c r="X621" t="n">
+        <v>150</v>
+      </c>
+      <c r="Y621" t="inlineStr">
+        <is>
+          <t>EXT Enhancements Roofing &amp; Siding LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>1216638107677105</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>saasGrowth</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Glenys Rodriguez Gomez</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr"/>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Dexter Tardy</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:43:55</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>2026-07-20 00:36:29</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>2026-07-20 00:36:26</t>
+        </is>
+      </c>
+      <c r="K622" t="b">
+        <v>1</v>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>TL Increase</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
         <is>
           <t xml:space="preserve"> BBJF0221</t>
         </is>
       </c>
-      <c r="N616" t="inlineStr">
+      <c r="N622" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="O616" t="inlineStr">
+      <c r="O622" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="P616" t="n">
+      <c r="P622" t="n">
         <v>250</v>
       </c>
-      <c r="Q616" t="n">
+      <c r="Q622" t="n">
         <v>400</v>
       </c>
-      <c r="R616" t="inlineStr">
+      <c r="R622" t="inlineStr">
         <is>
           <t>Glenys Rodriguez Gomez</t>
         </is>
       </c>
-      <c r="S616" t="inlineStr">
+      <c r="S622" t="inlineStr">
         <is>
           <t>Reoccurring Charge</t>
         </is>
       </c>
-      <c r="T616" t="inlineStr">
+      <c r="T622" t="inlineStr">
         <is>
           <t>Recommendation sent via email and closed by BA</t>
         </is>
       </c>
-      <c r="U616" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V616" t="inlineStr">
+      <c r="U622" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V622" t="inlineStr">
         <is>
           <t>CER was closed already</t>
         </is>
       </c>
-      <c r="W616" t="inlineStr">
+      <c r="W622" t="inlineStr">
         <is>
           <t>CC_1C03CA819</t>
         </is>
       </c>
-      <c r="X616" t="n">
+      <c r="X622" t="n">
         <v>10</v>
       </c>
-      <c r="Y616" t="inlineStr">
+      <c r="Y622" t="inlineStr">
         <is>
           <t>Pizza And Stuff</t>
         </is>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3344,11 +3344,7 @@
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>2026-07-28 18:02:34</t>
@@ -3357,7 +3353,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-07-30 09:33:33</t>
+          <t>2026-08-08 17:51:59</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3455,11 +3451,7 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>2026-07-29 08:33:52</t>
@@ -3468,7 +3460,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-07-30 09:31:38</t>
+          <t>2026-08-08 17:51:58</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3899,11 +3891,7 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>2026-07-23 17:43:27</t>
@@ -3912,7 +3900,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-07-29 15:19:16</t>
+          <t>2026-08-08 17:52:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4010,11 +3998,7 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>2026-07-28 17:37:03</t>
@@ -4023,7 +4007,7 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-07-29 15:19:16</t>
+          <t>2026-08-08 17:51:59</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4351,11 +4335,7 @@
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>2026-07-24 06:06:29</t>
@@ -4364,7 +4344,7 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-07-29 15:19:15</t>
+          <t>2026-08-08 17:51:59</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4795,11 +4775,7 @@
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>2026-07-27 00:10:51</t>
@@ -4808,7 +4784,7 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-29 15:19:15</t>
+          <t>2026-08-08 17:51:59</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -6375,11 +6351,7 @@
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>2026-07-20 21:13:35</t>
@@ -6388,7 +6360,7 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-07-27 10:22:54</t>
+          <t>2026-08-08 17:52:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6825,11 +6797,7 @@
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>2026-07-23 17:37:58</t>
@@ -6838,7 +6806,7 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-07-27 10:22:54</t>
+          <t>2026-08-08 17:51:59</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8272,11 +8240,7 @@
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>2026-07-14 19:26:38</t>
@@ -8285,7 +8249,7 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-07-17 10:48:43</t>
+          <t>2026-08-08 17:52:00</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8938,11 +8902,7 @@
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>2026-07-16 17:37:35</t>
@@ -8951,7 +8911,7 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-07-17 10:48:42</t>
+          <t>2026-08-08 17:52:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9049,11 +9009,7 @@
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>2026-07-08 04:42:37</t>
@@ -9062,7 +9018,7 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-07-13 06:00:22</t>
+          <t>2026-08-08 17:52:00</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10936,11 +10892,7 @@
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>2026-07-03 03:54:50</t>
@@ -10949,7 +10901,7 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-07-07 16:19:25</t>
+          <t>2026-08-08 17:52:00</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11156,11 +11108,7 @@
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>2026-06-29 22:50:30</t>
@@ -11169,7 +11117,7 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-07-01 16:17:18</t>
+          <t>2026-08-08 17:52:06</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11265,11 +11213,7 @@
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>2026-07-01 02:05:10</t>
@@ -11278,7 +11222,7 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-07-01 16:17:18</t>
+          <t>2026-08-08 17:52:02</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12258,11 +12202,7 @@
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>2026-07-01 04:54:59</t>
@@ -12271,7 +12211,7 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-07-03 03:51:02</t>
+          <t>2026-08-08 17:52:02</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12920,11 +12860,7 @@
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>2026-06-16 23:11:45</t>
@@ -12933,7 +12869,7 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-07-01 16:17:18</t>
+          <t>2026-08-08 17:52:08</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13695,11 +13631,7 @@
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>2026-06-29 22:44:06</t>
@@ -13708,7 +13640,7 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-07-01 16:17:17</t>
+          <t>2026-08-08 17:52:06</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -14137,11 +14069,7 @@
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>2026-06-23 04:18:14</t>
@@ -14150,7 +14078,7 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-07-01 16:17:17</t>
+          <t>2026-08-08 17:52:07</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -15578,11 +15506,7 @@
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>2026-06-29 23:05:22</t>
@@ -15591,7 +15515,7 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-07-01 16:17:17</t>
+          <t>2026-08-08 17:52:06</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15687,11 +15611,7 @@
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>2026-06-29 18:36:52</t>
@@ -15700,7 +15620,7 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-07-01 16:17:17</t>
+          <t>2026-08-08 17:52:07</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15907,11 +15827,7 @@
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>2026-06-07 21:58:39</t>
@@ -15920,7 +15836,7 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-06-18 16:08:10</t>
+          <t>2026-08-08 17:52:08</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -18230,11 +18146,7 @@
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
           <t>2026-06-03 01:19:37</t>
@@ -18243,7 +18155,7 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-06-08 06:32:17</t>
+          <t>2026-08-08 17:52:09</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -28648,11 +28560,7 @@
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
           <t>2026-05-05 23:47:42</t>
@@ -28661,7 +28569,7 @@
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2026-05-09 11:59:13</t>
+          <t>2026-08-08 17:52:09</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -29298,11 +29206,7 @@
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
           <t>2026-05-05 21:44:05</t>
@@ -29311,7 +29215,7 @@
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr">
         <is>
-          <t>2026-05-09 11:59:12</t>
+          <t>2026-08-08 17:52:09</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -29518,11 +29422,7 @@
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
           <t>2026-05-05 22:35:34</t>
@@ -29531,7 +29431,7 @@
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr">
         <is>
-          <t>2026-05-09 11:59:12</t>
+          <t>2026-08-08 17:52:09</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -29629,11 +29529,7 @@
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
           <t>2026-05-05 22:31:18</t>
@@ -29642,7 +29538,7 @@
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
-          <t>2026-05-09 11:59:12</t>
+          <t>2026-08-08 17:52:09</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -30295,11 +30191,7 @@
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
           <t>2026-05-06 01:32:26</t>
@@ -30308,7 +30200,7 @@
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr">
         <is>
-          <t>2026-05-09 11:59:12</t>
+          <t>2026-08-08 17:52:09</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -30406,11 +30298,7 @@
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
           <t>2026-05-05 21:40:03</t>
@@ -30419,7 +30307,7 @@
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
-          <t>2026-05-09 11:59:12</t>
+          <t>2026-08-08 17:52:10</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -31070,11 +30958,7 @@
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
           <t>2026-04-22 23:51:00</t>
@@ -31083,7 +30967,7 @@
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr">
         <is>
-          <t>2026-05-02 06:59:36</t>
+          <t>2026-08-08 17:52:30</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -35395,11 +35279,7 @@
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr">
         <is>
           <t>2026-03-10 20:03:06</t>
@@ -35506,11 +35386,7 @@
         </is>
       </c>
       <c r="E317" t="inlineStr"/>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F317" t="inlineStr"/>
       <c r="G317" t="inlineStr">
         <is>
           <t>2026-03-18 08:37:25</t>
@@ -35617,11 +35493,7 @@
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr">
         <is>
           <t>2026-03-26 03:32:08</t>
@@ -37833,11 +37705,7 @@
         </is>
       </c>
       <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
           <t>2026-03-26 03:37:44</t>
@@ -38164,11 +38032,7 @@
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>Julian Komimbin</t>
-        </is>
-      </c>
+      <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
           <t>2026-03-31 17:16:19</t>

--- a/data.xlsx
+++ b/data.xlsx
@@ -676,11 +676,7 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2026-08-06 09:37:55</t>
@@ -693,7 +689,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-24 12:55:05</t>
+          <t>2026-08-25 23:40:14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1132,11 +1128,7 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2026-08-10 20:48:31</t>
@@ -1145,7 +1137,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-21 08:30:07</t>
+          <t>2026-08-25 23:40:13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1243,11 +1235,7 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2026-08-10 20:42:34</t>
@@ -1256,7 +1244,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-08-21 08:18:13</t>
+          <t>2026-08-25 23:40:13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -4345,11 +4333,7 @@
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>2026-07-27 18:30:43</t>
@@ -4362,7 +4346,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-08-10 17:47:03</t>
+          <t>2026-08-25 23:40:15</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -6912,11 +6896,7 @@
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>2026-07-23 11:01:56</t>
@@ -6925,7 +6905,7 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-07-31 16:44:18</t>
+          <t>2026-08-25 23:40:15</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7021,11 +7001,7 @@
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>2026-07-23 16:40:35</t>
@@ -7034,7 +7010,7 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-07-31 16:43:28</t>
+          <t>2026-08-25 23:40:15</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -9556,11 +9532,7 @@
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>2026-07-02 15:53:18</t>
@@ -9573,7 +9545,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-07-27 10:22:55</t>
+          <t>2026-08-25 23:40:16</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -11025,11 +10997,7 @@
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>2026-07-21 10:54:06</t>
@@ -11042,7 +11010,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-07-27 14:39:27</t>
+          <t>2026-08-25 23:40:15</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -13566,11 +13534,7 @@
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>2026-06-23 15:38:04</t>
@@ -13583,7 +13547,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-07-08 05:40:44</t>
+          <t>2026-08-25 23:40:22</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -13681,11 +13645,7 @@
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>2026-06-29 18:35:56</t>
@@ -13698,7 +13658,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-07-08 05:40:44</t>
+          <t>2026-08-25 23:40:22</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13907,11 +13867,7 @@
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>2026-07-02 16:46:47</t>
@@ -13920,7 +13876,7 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-07-08 05:40:44</t>
+          <t>2026-08-25 23:40:16</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -14349,11 +14305,7 @@
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
           <t>2026-06-16 15:54:33</t>
@@ -14366,7 +14318,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-07-06 06:13:55</t>
+          <t>2026-08-25 23:40:22</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14454,11 +14406,7 @@
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
           <t>2026-06-30 18:16:53</t>
@@ -14471,7 +14419,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-07-07 16:59:39</t>
+          <t>2026-08-25 23:40:22</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14567,11 +14515,7 @@
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>2026-06-30 18:15:16</t>
@@ -14584,7 +14528,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-07-07 16:59:42</t>
+          <t>2026-08-25 23:40:22</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15770,11 +15714,7 @@
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>2026-06-11 11:38:49</t>
@@ -15783,7 +15723,7 @@
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-07-01 16:17:18</t>
+          <t>2026-08-25 23:40:22</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -16212,11 +16152,7 @@
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>2026-06-16 16:01:13</t>
@@ -16225,7 +16161,7 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-07-01 16:17:18</t>
+          <t>2026-08-25 23:40:22</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -20828,11 +20764,7 @@
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
           <t>2026-06-11 17:51:30</t>
@@ -20841,7 +20773,7 @@
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-06-15 06:28:51</t>
+          <t>2026-08-25 23:40:22</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -21270,11 +21202,7 @@
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
           <t>2026-06-08 10:48:59</t>
@@ -21283,7 +21211,7 @@
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-06-15 06:28:51</t>
+          <t>2026-08-25 23:40:23</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -23369,11 +23297,7 @@
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
           <t>2026-05-29 16:33:57</t>
@@ -23382,7 +23306,7 @@
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
-          <t>2026-06-05 12:14:12</t>
+          <t>2026-08-25 23:40:23</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -23478,11 +23402,7 @@
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
           <t>2026-05-29 16:36:07</t>
@@ -23491,7 +23411,7 @@
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2026-06-05 12:14:12</t>
+          <t>2026-08-25 23:40:23</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -25141,11 +25061,7 @@
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
           <t>2026-05-11 18:22:00</t>
@@ -25154,7 +25070,7 @@
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2026-05-30 11:40:30</t>
+          <t>2026-08-25 23:40:23</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -25250,11 +25166,7 @@
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
           <t>2026-05-07 15:57:28</t>
@@ -25263,7 +25175,7 @@
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2026-05-30 11:40:30</t>
+          <t>2026-08-25 23:40:23</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -25359,11 +25271,7 @@
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
           <t>2026-05-07 15:59:35</t>
@@ -25372,7 +25280,7 @@
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2026-05-30 11:40:30</t>
+          <t>2026-08-25 23:40:23</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -25468,11 +25376,7 @@
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
           <t>2026-05-19 18:10:53</t>
@@ -25481,7 +25385,7 @@
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2026-05-30 11:40:30</t>
+          <t>2026-08-25 23:40:23</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -33008,11 +32912,7 @@
         </is>
       </c>
       <c r="E295" t="inlineStr"/>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr">
         <is>
           <t>2026-05-01 08:28:22</t>
@@ -33021,7 +32921,7 @@
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
-          <t>2026-05-09 11:59:13</t>
+          <t>2026-08-25 23:40:23</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -33224,11 +33124,7 @@
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr">
         <is>
           <t>2026-04-22 11:21:31</t>
@@ -33237,7 +33133,7 @@
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
-          <t>2026-05-09 11:59:12</t>
+          <t>2026-08-25 23:40:27</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -33329,11 +33225,7 @@
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr">
         <is>
           <t>2026-04-27 09:00:23</t>
@@ -33342,7 +33234,7 @@
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
-          <t>2026-05-09 11:59:12</t>
+          <t>2026-08-25 23:40:24</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -41717,11 +41609,7 @@
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F374" t="inlineStr"/>
       <c r="G374" t="inlineStr">
         <is>
           <t>2026-02-06 14:18:11</t>
@@ -41826,11 +41714,7 @@
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>Carla Miner-Luginbyhl</t>
-        </is>
-      </c>
+      <c r="F375" t="inlineStr"/>
       <c r="G375" t="inlineStr">
         <is>
           <t>2026-03-03 15:00:46</t>
